--- a/Critical Raw Materials List.xlsx
+++ b/Critical Raw Materials List.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4659,7 @@
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>07-05-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5584,7 +5584,7 @@
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5609,7 +5609,7 @@
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>07-05-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6009,7 +6009,7 @@
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6084,7 @@
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="E241" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="E242" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="E243" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="E247" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="E248" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6659,7 +6659,7 @@
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6709,7 +6709,7 @@
       </c>
       <c r="E251" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="E253" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="E255" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6859,7 +6859,7 @@
       </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="E258" s="3" t="inlineStr">
         <is>
-          <t>07-05-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="E259" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="E260" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6959,7 +6959,7 @@
       </c>
       <c r="E261" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="E263" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="E264" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="E265" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7084,7 +7084,7 @@
       </c>
       <c r="E266" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="E267" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="E268" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
       </c>
       <c r="E269" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
       </c>
       <c r="E270" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="E271" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="E272" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="E273" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="E274" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="E275" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="E276" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7359,7 @@
       </c>
       <c r="E277" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="E278" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7409,7 +7409,7 @@
       </c>
       <c r="E279" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="E280" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="E281" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="E282" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7509,7 +7509,7 @@
       </c>
       <c r="E283" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7534,7 +7534,7 @@
       </c>
       <c r="E284" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="E285" s="3" t="inlineStr">
         <is>
-          <t>07-05-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7584,7 +7584,7 @@
       </c>
       <c r="E286" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="E287" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="E288" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="E289" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="E290" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="E291" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="E292" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7759,7 +7759,7 @@
       </c>
       <c r="E293" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7784,7 +7784,7 @@
       </c>
       <c r="E294" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="E295" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="E296" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="E297" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="E298" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="E299" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="E300" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="E301" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="E302" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="E303" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="E304" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="E305" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="E306" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8109,7 +8109,7 @@
       </c>
       <c r="E307" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="E308" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="E309" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="E310" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8209,7 +8209,7 @@
       </c>
       <c r="E311" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="E312" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="E313" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="E314" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="E315" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="E316" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="E317" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="E318" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8409,7 +8409,7 @@
       </c>
       <c r="E319" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="E320" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="E321" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="E322" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="E323" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="E324" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8559,7 +8559,7 @@
       </c>
       <c r="E325" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8584,7 +8584,7 @@
       </c>
       <c r="E326" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8609,7 +8609,7 @@
       </c>
       <c r="E327" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="E328" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="E329" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8684,7 +8684,7 @@
       </c>
       <c r="E330" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8709,7 +8709,7 @@
       </c>
       <c r="E331" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8734,7 +8734,7 @@
       </c>
       <c r="E332" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8759,7 +8759,7 @@
       </c>
       <c r="E333" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="E334" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8809,7 +8809,7 @@
       </c>
       <c r="E335" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="E336" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8859,7 +8859,7 @@
       </c>
       <c r="E337" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8884,7 +8884,7 @@
       </c>
       <c r="E338" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8909,7 +8909,7 @@
       </c>
       <c r="E339" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="E340" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="E341" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8984,7 +8984,7 @@
       </c>
       <c r="E342" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9009,7 +9009,7 @@
       </c>
       <c r="E343" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="E344" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9059,7 +9059,7 @@
       </c>
       <c r="E345" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9084,7 +9084,7 @@
       </c>
       <c r="E346" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="E347" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="E348" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9159,7 +9159,7 @@
       </c>
       <c r="E349" s="3" t="inlineStr">
         <is>
-          <t>07-05-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9184,7 +9184,7 @@
       </c>
       <c r="E350" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9209,7 +9209,7 @@
       </c>
       <c r="E351" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="E352" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9259,7 +9259,7 @@
       </c>
       <c r="E353" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="E354" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9309,7 +9309,7 @@
       </c>
       <c r="E355" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="E356" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="E357" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9384,7 +9384,7 @@
       </c>
       <c r="E358" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9409,7 +9409,7 @@
       </c>
       <c r="E359" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9434,7 +9434,7 @@
       </c>
       <c r="E360" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9459,7 +9459,7 @@
       </c>
       <c r="E361" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9484,7 +9484,7 @@
       </c>
       <c r="E362" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="E363" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="E364" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9559,7 +9559,7 @@
       </c>
       <c r="E365" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9584,7 +9584,7 @@
       </c>
       <c r="E366" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="E367" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9634,7 +9634,7 @@
       </c>
       <c r="E368" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9659,7 +9659,7 @@
       </c>
       <c r="E369" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9684,7 +9684,7 @@
       </c>
       <c r="E370" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="E371" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="E372" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="E373" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="E374" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="E375" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="E376" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9859,7 +9859,7 @@
       </c>
       <c r="E377" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9884,7 +9884,7 @@
       </c>
       <c r="E378" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9909,7 +9909,7 @@
       </c>
       <c r="E379" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="E380" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
       </c>
       <c r="E381" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9984,7 +9984,7 @@
       </c>
       <c r="E382" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="E383" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10034,7 +10034,7 @@
       </c>
       <c r="E384" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10059,7 +10059,7 @@
       </c>
       <c r="E385" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="E386" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10109,7 +10109,7 @@
       </c>
       <c r="E387" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10134,7 +10134,7 @@
       </c>
       <c r="E388" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10159,7 +10159,7 @@
       </c>
       <c r="E389" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10184,7 +10184,7 @@
       </c>
       <c r="E390" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="E391" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10234,7 +10234,7 @@
       </c>
       <c r="E392" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="E393" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10284,7 +10284,7 @@
       </c>
       <c r="E394" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10309,7 +10309,7 @@
       </c>
       <c r="E395" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="E396" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10359,7 +10359,7 @@
       </c>
       <c r="E397" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="E398" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10409,7 +10409,7 @@
       </c>
       <c r="E399" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="E400" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10459,7 +10459,7 @@
       </c>
       <c r="E401" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10484,7 +10484,7 @@
       </c>
       <c r="E402" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10509,7 +10509,7 @@
       </c>
       <c r="E403" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="E404" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10559,7 +10559,7 @@
       </c>
       <c r="E405" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="E406" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10609,7 +10609,7 @@
       </c>
       <c r="E407" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="E408" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10659,7 +10659,7 @@
       </c>
       <c r="E409" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10684,7 +10684,7 @@
       </c>
       <c r="E410" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10709,7 +10709,7 @@
       </c>
       <c r="E411" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10734,7 +10734,7 @@
       </c>
       <c r="E412" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10759,7 +10759,7 @@
       </c>
       <c r="E413" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10784,7 +10784,7 @@
       </c>
       <c r="E414" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10809,7 +10809,7 @@
       </c>
       <c r="E415" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10834,7 +10834,7 @@
       </c>
       <c r="E416" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="E417" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10884,7 +10884,7 @@
       </c>
       <c r="E418" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="E419" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="E420" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10959,7 +10959,7 @@
       </c>
       <c r="E421" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10984,7 +10984,7 @@
       </c>
       <c r="E422" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="E423" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="E424" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11059,7 +11059,7 @@
       </c>
       <c r="E425" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11084,7 +11084,7 @@
       </c>
       <c r="E426" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11109,7 +11109,7 @@
       </c>
       <c r="E427" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11134,7 +11134,7 @@
       </c>
       <c r="E428" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11159,7 +11159,7 @@
       </c>
       <c r="E429" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11184,7 +11184,7 @@
       </c>
       <c r="E430" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11209,7 +11209,7 @@
       </c>
       <c r="E431" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="E432" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11259,7 @@
       </c>
       <c r="E433" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11284,7 +11284,7 @@
       </c>
       <c r="E434" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11309,7 +11309,7 @@
       </c>
       <c r="E435" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11334,7 +11334,7 @@
       </c>
       <c r="E436" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="E437" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11384,7 +11384,7 @@
       </c>
       <c r="E438" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11409,7 +11409,7 @@
       </c>
       <c r="E439" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11434,7 +11434,7 @@
       </c>
       <c r="E440" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11459,7 +11459,7 @@
       </c>
       <c r="E441" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11484,7 +11484,7 @@
       </c>
       <c r="E442" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11509,7 +11509,7 @@
       </c>
       <c r="E443" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11534,7 +11534,7 @@
       </c>
       <c r="E444" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11559,7 +11559,7 @@
       </c>
       <c r="E445" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11584,7 +11584,7 @@
       </c>
       <c r="E446" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="E447" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11634,7 +11634,7 @@
       </c>
       <c r="E448" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="E449" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11684,7 +11684,7 @@
       </c>
       <c r="E450" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="E451" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="E452" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11759,7 +11759,7 @@
       </c>
       <c r="E453" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="E454" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="E455" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11834,7 +11834,7 @@
       </c>
       <c r="E456" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="E457" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="E458" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11909,7 +11909,7 @@
       </c>
       <c r="E459" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="E460" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11959,7 +11959,7 @@
       </c>
       <c r="E461" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11984,7 +11984,7 @@
       </c>
       <c r="E462" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12009,7 +12009,7 @@
       </c>
       <c r="E463" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="E464" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12059,7 +12059,7 @@
       </c>
       <c r="E465" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12084,7 +12084,7 @@
       </c>
       <c r="E466" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12109,7 +12109,7 @@
       </c>
       <c r="E467" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12134,7 +12134,7 @@
       </c>
       <c r="E468" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12159,7 +12159,7 @@
       </c>
       <c r="E469" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12184,7 +12184,7 @@
       </c>
       <c r="E470" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12209,7 +12209,7 @@
       </c>
       <c r="E471" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12234,7 +12234,7 @@
       </c>
       <c r="E472" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12259,7 +12259,7 @@
       </c>
       <c r="E473" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12284,7 +12284,7 @@
       </c>
       <c r="E474" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12309,7 +12309,7 @@
       </c>
       <c r="E475" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12334,7 +12334,7 @@
       </c>
       <c r="E476" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12359,7 +12359,7 @@
       </c>
       <c r="E477" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12384,7 +12384,7 @@
       </c>
       <c r="E478" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12409,7 +12409,7 @@
       </c>
       <c r="E479" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12434,7 +12434,7 @@
       </c>
       <c r="E480" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="E481" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12484,7 +12484,7 @@
       </c>
       <c r="E482" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12509,7 +12509,7 @@
       </c>
       <c r="E483" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12534,7 @@
       </c>
       <c r="E484" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="E485" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12584,7 +12584,7 @@
       </c>
       <c r="E486" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12609,7 +12609,7 @@
       </c>
       <c r="E487" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="E488" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="E489" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12684,7 +12684,7 @@
       </c>
       <c r="E490" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12709,7 +12709,7 @@
       </c>
       <c r="E491" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12734,7 +12734,7 @@
       </c>
       <c r="E492" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="E493" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12784,7 +12784,7 @@
       </c>
       <c r="E494" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12809,7 +12809,7 @@
       </c>
       <c r="E495" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12834,7 +12834,7 @@
       </c>
       <c r="E496" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="E497" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="E498" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12909,7 +12909,7 @@
       </c>
       <c r="E499" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12934,7 +12934,7 @@
       </c>
       <c r="E500" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12959,7 +12959,7 @@
       </c>
       <c r="E501" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12984,7 +12984,7 @@
       </c>
       <c r="E502" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13009,7 +13009,7 @@
       </c>
       <c r="E503" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13034,7 +13034,7 @@
       </c>
       <c r="E504" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13059,7 +13059,7 @@
       </c>
       <c r="E505" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13084,7 +13084,7 @@
       </c>
       <c r="E506" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13109,7 +13109,7 @@
       </c>
       <c r="E507" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13134,7 +13134,7 @@
       </c>
       <c r="E508" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13159,7 +13159,7 @@
       </c>
       <c r="E509" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="E510" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13209,7 +13209,7 @@
       </c>
       <c r="E511" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13234,7 +13234,7 @@
       </c>
       <c r="E512" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13259,7 +13259,7 @@
       </c>
       <c r="E513" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13284,7 +13284,7 @@
       </c>
       <c r="E514" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13309,7 +13309,7 @@
       </c>
       <c r="E515" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="E516" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13359,7 +13359,7 @@
       </c>
       <c r="E517" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13384,7 +13384,7 @@
       </c>
       <c r="E518" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13409,7 +13409,7 @@
       </c>
       <c r="E519" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13434,7 +13434,7 @@
       </c>
       <c r="E520" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13459,7 +13459,7 @@
       </c>
       <c r="E521" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13484,7 +13484,7 @@
       </c>
       <c r="E522" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="E523" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13534,7 +13534,7 @@
       </c>
       <c r="E524" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13559,7 +13559,7 @@
       </c>
       <c r="E525" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13584,7 +13584,7 @@
       </c>
       <c r="E526" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13609,7 +13609,7 @@
       </c>
       <c r="E527" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="E528" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13659,7 +13659,7 @@
       </c>
       <c r="E529" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13684,7 +13684,7 @@
       </c>
       <c r="E530" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13709,7 +13709,7 @@
       </c>
       <c r="E531" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13734,7 +13734,7 @@
       </c>
       <c r="E532" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13759,7 +13759,7 @@
       </c>
       <c r="E533" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13784,7 +13784,7 @@
       </c>
       <c r="E534" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13809,7 +13809,7 @@
       </c>
       <c r="E535" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13834,7 +13834,7 @@
       </c>
       <c r="E536" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13859,7 +13859,7 @@
       </c>
       <c r="E537" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13884,7 +13884,7 @@
       </c>
       <c r="E538" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13909,7 +13909,7 @@
       </c>
       <c r="E539" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13934,7 +13934,7 @@
       </c>
       <c r="E540" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13959,7 +13959,7 @@
       </c>
       <c r="E541" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13984,7 +13984,7 @@
       </c>
       <c r="E542" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14009,7 +14009,7 @@
       </c>
       <c r="E543" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="E544" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14059,7 +14059,7 @@
       </c>
       <c r="E545" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14084,7 +14084,7 @@
       </c>
       <c r="E546" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="E547" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14134,7 +14134,7 @@
       </c>
       <c r="E548" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="E549" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14184,7 +14184,7 @@
       </c>
       <c r="E550" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14209,7 +14209,7 @@
       </c>
       <c r="E551" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14234,7 +14234,7 @@
       </c>
       <c r="E552" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14259,7 +14259,7 @@
       </c>
       <c r="E553" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="E554" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14309,7 +14309,7 @@
       </c>
       <c r="E555" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14334,7 +14334,7 @@
       </c>
       <c r="E556" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14359,7 +14359,7 @@
       </c>
       <c r="E557" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14384,7 +14384,7 @@
       </c>
       <c r="E558" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14409,7 @@
       </c>
       <c r="E559" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14434,7 +14434,7 @@
       </c>
       <c r="E560" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14459,7 +14459,7 @@
       </c>
       <c r="E561" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="E562" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14509,7 +14509,7 @@
       </c>
       <c r="E563" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="E564" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14559,7 +14559,7 @@
       </c>
       <c r="E565" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14584,7 +14584,7 @@
       </c>
       <c r="E566" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14609,7 +14609,7 @@
       </c>
       <c r="E567" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14634,7 +14634,7 @@
       </c>
       <c r="E568" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14659,7 +14659,7 @@
       </c>
       <c r="E569" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14684,7 +14684,7 @@
       </c>
       <c r="E570" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14709,7 +14709,7 @@
       </c>
       <c r="E571" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="E572" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14759,7 +14759,7 @@
       </c>
       <c r="E573" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="E574" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="E575" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="E576" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14859,7 +14859,7 @@
       </c>
       <c r="E577" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14884,7 +14884,7 @@
       </c>
       <c r="E578" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14909,7 +14909,7 @@
       </c>
       <c r="E579" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14934,7 +14934,7 @@
       </c>
       <c r="E580" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14959,7 +14959,7 @@
       </c>
       <c r="E581" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="E582" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15009,7 +15009,7 @@
       </c>
       <c r="E583" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15034,7 +15034,7 @@
       </c>
       <c r="E584" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15059,7 +15059,7 @@
       </c>
       <c r="E585" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15084,7 +15084,7 @@
       </c>
       <c r="E586" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15109,7 +15109,7 @@
       </c>
       <c r="E587" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="E588" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15159,7 +15159,7 @@
       </c>
       <c r="E589" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15184,7 +15184,7 @@
       </c>
       <c r="E590" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15209,7 +15209,7 @@
       </c>
       <c r="E591" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15234,7 +15234,7 @@
       </c>
       <c r="E592" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15259,7 +15259,7 @@
       </c>
       <c r="E593" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15284,7 +15284,7 @@
       </c>
       <c r="E594" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15309,7 +15309,7 @@
       </c>
       <c r="E595" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15334,7 +15334,7 @@
       </c>
       <c r="E596" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15359,7 +15359,7 @@
       </c>
       <c r="E597" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15384,7 +15384,7 @@
       </c>
       <c r="E598" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="E599" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="E600" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15459,7 @@
       </c>
       <c r="E601" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="E602" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15509,7 +15509,7 @@
       </c>
       <c r="E603" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15534,7 +15534,7 @@
       </c>
       <c r="E604" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15559,7 +15559,7 @@
       </c>
       <c r="E605" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15584,7 +15584,7 @@
       </c>
       <c r="E606" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15609,7 +15609,7 @@
       </c>
       <c r="E607" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15634,7 +15634,7 @@
       </c>
       <c r="E608" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15659,7 +15659,7 @@
       </c>
       <c r="E609" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15684,7 +15684,7 @@
       </c>
       <c r="E610" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15709,7 +15709,7 @@
       </c>
       <c r="E611" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="E612" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15759,7 +15759,7 @@
       </c>
       <c r="E613" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15784,7 +15784,7 @@
       </c>
       <c r="E614" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15809,7 +15809,7 @@
       </c>
       <c r="E615" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15834,7 +15834,7 @@
       </c>
       <c r="E616" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15859,7 +15859,7 @@
       </c>
       <c r="E617" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="E618" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15909,7 +15909,7 @@
       </c>
       <c r="E619" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15934,7 +15934,7 @@
       </c>
       <c r="E620" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15959,7 +15959,7 @@
       </c>
       <c r="E621" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="E622" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16009,7 +16009,7 @@
       </c>
       <c r="E623" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16034,7 +16034,7 @@
       </c>
       <c r="E624" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16059,7 +16059,7 @@
       </c>
       <c r="E625" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16084,7 +16084,7 @@
       </c>
       <c r="E626" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16109,7 +16109,7 @@
       </c>
       <c r="E627" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="E628" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="E629" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16184,7 +16184,7 @@
       </c>
       <c r="E630" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16209,7 +16209,7 @@
       </c>
       <c r="E631" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16234,7 +16234,7 @@
       </c>
       <c r="E632" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16259,7 +16259,7 @@
       </c>
       <c r="E633" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16284,7 +16284,7 @@
       </c>
       <c r="E634" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16309,7 +16309,7 @@
       </c>
       <c r="E635" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16334,7 +16334,7 @@
       </c>
       <c r="E636" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16359,7 +16359,7 @@
       </c>
       <c r="E637" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16384,7 +16384,7 @@
       </c>
       <c r="E638" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16409,7 +16409,7 @@
       </c>
       <c r="E639" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="E640" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16459,7 +16459,7 @@
       </c>
       <c r="E641" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16484,7 +16484,7 @@
       </c>
       <c r="E642" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16509,7 +16509,7 @@
       </c>
       <c r="E643" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16534,7 +16534,7 @@
       </c>
       <c r="E644" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="E645" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16584,7 +16584,7 @@
       </c>
       <c r="E646" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16609,7 +16609,7 @@
       </c>
       <c r="E647" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="E648" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16659,7 +16659,7 @@
       </c>
       <c r="E649" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16684,7 +16684,7 @@
       </c>
       <c r="E650" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16709,7 +16709,7 @@
       </c>
       <c r="E651" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16734,7 +16734,7 @@
       </c>
       <c r="E652" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16759,7 +16759,7 @@
       </c>
       <c r="E653" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="E654" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="E655" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="E656" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16859,7 +16859,7 @@
       </c>
       <c r="E657" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16884,7 +16884,7 @@
       </c>
       <c r="E658" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16909,7 +16909,7 @@
       </c>
       <c r="E659" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16934,7 +16934,7 @@
       </c>
       <c r="E660" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16959,7 +16959,7 @@
       </c>
       <c r="E661" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16984,7 +16984,7 @@
       </c>
       <c r="E662" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17009,7 +17009,7 @@
       </c>
       <c r="E663" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17034,7 +17034,7 @@
       </c>
       <c r="E664" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17059,7 +17059,7 @@
       </c>
       <c r="E665" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17084,7 +17084,7 @@
       </c>
       <c r="E666" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17109,7 +17109,7 @@
       </c>
       <c r="E667" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17134,7 +17134,7 @@
       </c>
       <c r="E668" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17159,7 +17159,7 @@
       </c>
       <c r="E669" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="E670" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17209,7 +17209,7 @@
       </c>
       <c r="E671" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17234,7 +17234,7 @@
       </c>
       <c r="E672" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17259,7 +17259,7 @@
       </c>
       <c r="E673" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17284,7 +17284,7 @@
       </c>
       <c r="E674" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17309,7 +17309,7 @@
       </c>
       <c r="E675" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17334,7 +17334,7 @@
       </c>
       <c r="E676" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17359,7 +17359,7 @@
       </c>
       <c r="E677" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17384,7 +17384,7 @@
       </c>
       <c r="E678" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="E679" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17434,7 +17434,7 @@
       </c>
       <c r="E680" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17459,7 +17459,7 @@
       </c>
       <c r="E681" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="E682" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17509,7 +17509,7 @@
       </c>
       <c r="E683" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="E684" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17559,7 +17559,7 @@
       </c>
       <c r="E685" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17584,7 +17584,7 @@
       </c>
       <c r="E686" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17609,7 +17609,7 @@
       </c>
       <c r="E687" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="E688" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17659,7 +17659,7 @@
       </c>
       <c r="E689" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17684,7 +17684,7 @@
       </c>
       <c r="E690" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17709,7 +17709,7 @@
       </c>
       <c r="E691" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17734,7 +17734,7 @@
       </c>
       <c r="E692" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="E693" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17784,7 +17784,7 @@
       </c>
       <c r="E694" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17809,7 +17809,7 @@
       </c>
       <c r="E695" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17834,7 +17834,7 @@
       </c>
       <c r="E696" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17859,7 +17859,7 @@
       </c>
       <c r="E697" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17884,7 +17884,7 @@
       </c>
       <c r="E698" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17909,7 +17909,7 @@
       </c>
       <c r="E699" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17934,7 +17934,7 @@
       </c>
       <c r="E700" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17959,7 +17959,7 @@
       </c>
       <c r="E701" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17984,7 +17984,7 @@
       </c>
       <c r="E702" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18009,7 +18009,7 @@
       </c>
       <c r="E703" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18034,7 +18034,7 @@
       </c>
       <c r="E704" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18059,7 +18059,7 @@
       </c>
       <c r="E705" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18084,7 +18084,7 @@
       </c>
       <c r="E706" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18109,7 +18109,7 @@
       </c>
       <c r="E707" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18134,7 +18134,7 @@
       </c>
       <c r="E708" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18159,7 +18159,7 @@
       </c>
       <c r="E709" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18184,7 +18184,7 @@
       </c>
       <c r="E710" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18209,7 +18209,7 @@
       </c>
       <c r="E711" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="E712" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18259,7 +18259,7 @@
       </c>
       <c r="E713" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18284,7 +18284,7 @@
       </c>
       <c r="E714" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18309,7 +18309,7 @@
       </c>
       <c r="E715" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18334,7 +18334,7 @@
       </c>
       <c r="E716" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18359,7 +18359,7 @@
       </c>
       <c r="E717" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18384,7 +18384,7 @@
       </c>
       <c r="E718" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18409,7 +18409,7 @@
       </c>
       <c r="E719" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18434,7 +18434,7 @@
       </c>
       <c r="E720" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18459,7 +18459,7 @@
       </c>
       <c r="E721" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18484,7 +18484,7 @@
       </c>
       <c r="E722" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18509,7 +18509,7 @@
       </c>
       <c r="E723" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18534,7 +18534,7 @@
       </c>
       <c r="E724" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18559,7 +18559,7 @@
       </c>
       <c r="E725" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18584,7 +18584,7 @@
       </c>
       <c r="E726" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18609,7 +18609,7 @@
       </c>
       <c r="E727" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18634,7 +18634,7 @@
       </c>
       <c r="E728" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18659,7 +18659,7 @@
       </c>
       <c r="E729" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18684,7 +18684,7 @@
       </c>
       <c r="E730" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="E731" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18734,7 +18734,7 @@
       </c>
       <c r="E732" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18759,7 +18759,7 @@
       </c>
       <c r="E733" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18784,7 +18784,7 @@
       </c>
       <c r="E734" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="E735" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18834,7 +18834,7 @@
       </c>
       <c r="E736" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18859,7 +18859,7 @@
       </c>
       <c r="E737" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18884,7 +18884,7 @@
       </c>
       <c r="E738" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18909,7 +18909,7 @@
       </c>
       <c r="E739" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="E740" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18959,7 +18959,7 @@
       </c>
       <c r="E741" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18984,7 +18984,7 @@
       </c>
       <c r="E742" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19009,7 +19009,7 @@
       </c>
       <c r="E743" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="E744" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19059,7 +19059,7 @@
       </c>
       <c r="E745" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19084,7 +19084,7 @@
       </c>
       <c r="E746" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19109,7 +19109,7 @@
       </c>
       <c r="E747" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19134,7 +19134,7 @@
       </c>
       <c r="E748" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19159,7 +19159,7 @@
       </c>
       <c r="E749" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19184,7 +19184,7 @@
       </c>
       <c r="E750" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="E751" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19234,7 +19234,7 @@
       </c>
       <c r="E752" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19259,7 +19259,7 @@
       </c>
       <c r="E753" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19284,7 +19284,7 @@
       </c>
       <c r="E754" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19309,7 +19309,7 @@
       </c>
       <c r="E755" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19334,7 +19334,7 @@
       </c>
       <c r="E756" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="E757" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19384,7 +19384,7 @@
       </c>
       <c r="E758" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19409,7 +19409,7 @@
       </c>
       <c r="E759" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19434,7 +19434,7 @@
       </c>
       <c r="E760" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19459,7 +19459,7 @@
       </c>
       <c r="E761" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19484,7 +19484,7 @@
       </c>
       <c r="E762" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19509,7 +19509,7 @@
       </c>
       <c r="E763" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19534,7 +19534,7 @@
       </c>
       <c r="E764" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="E765" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19584,7 +19584,7 @@
       </c>
       <c r="E766" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19609,7 +19609,7 @@
       </c>
       <c r="E767" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="E768" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19659,7 +19659,7 @@
       </c>
       <c r="E769" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="E770" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19709,7 +19709,7 @@
       </c>
       <c r="E771" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19734,7 +19734,7 @@
       </c>
       <c r="E772" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="E773" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19784,7 +19784,7 @@
       </c>
       <c r="E774" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19809,7 +19809,7 @@
       </c>
       <c r="E775" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19834,7 +19834,7 @@
       </c>
       <c r="E776" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19859,7 +19859,7 @@
       </c>
       <c r="E777" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="E778" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19909,7 +19909,7 @@
       </c>
       <c r="E779" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19934,7 +19934,7 @@
       </c>
       <c r="E780" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19959,7 +19959,7 @@
       </c>
       <c r="E781" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19984,7 +19984,7 @@
       </c>
       <c r="E782" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20009,7 +20009,7 @@
       </c>
       <c r="E783" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20034,7 +20034,7 @@
       </c>
       <c r="E784" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="E785" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20084,7 +20084,7 @@
       </c>
       <c r="E786" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20109,7 +20109,7 @@
       </c>
       <c r="E787" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20134,7 +20134,7 @@
       </c>
       <c r="E788" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20159,7 +20159,7 @@
       </c>
       <c r="E789" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20184,7 +20184,7 @@
       </c>
       <c r="E790" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20209,7 +20209,7 @@
       </c>
       <c r="E791" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20234,7 +20234,7 @@
       </c>
       <c r="E792" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20259,7 +20259,7 @@
       </c>
       <c r="E793" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20284,7 +20284,7 @@
       </c>
       <c r="E794" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20309,7 +20309,7 @@
       </c>
       <c r="E795" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="E796" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20359,7 +20359,7 @@
       </c>
       <c r="E797" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="E798" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20409,7 +20409,7 @@
       </c>
       <c r="E799" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20434,7 +20434,7 @@
       </c>
       <c r="E800" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20459,7 +20459,7 @@
       </c>
       <c r="E801" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20484,7 +20484,7 @@
       </c>
       <c r="E802" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20509,7 +20509,7 @@
       </c>
       <c r="E803" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20534,7 +20534,7 @@
       </c>
       <c r="E804" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20559,7 +20559,7 @@
       </c>
       <c r="E805" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20584,7 +20584,7 @@
       </c>
       <c r="E806" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20609,7 +20609,7 @@
       </c>
       <c r="E807" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20634,7 +20634,7 @@
       </c>
       <c r="E808" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="E809" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20684,7 +20684,7 @@
       </c>
       <c r="E810" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20709,7 +20709,7 @@
       </c>
       <c r="E811" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="E812" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20759,7 +20759,7 @@
       </c>
       <c r="E813" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20784,7 +20784,7 @@
       </c>
       <c r="E814" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20809,7 +20809,7 @@
       </c>
       <c r="E815" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="E816" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20859,7 +20859,7 @@
       </c>
       <c r="E817" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20884,7 +20884,7 @@
       </c>
       <c r="E818" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20909,7 +20909,7 @@
       </c>
       <c r="E819" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20934,7 +20934,7 @@
       </c>
       <c r="E820" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20959,7 +20959,7 @@
       </c>
       <c r="E821" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20984,7 +20984,7 @@
       </c>
       <c r="E822" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21009,7 +21009,7 @@
       </c>
       <c r="E823" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="E824" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21059,7 +21059,7 @@
       </c>
       <c r="E825" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21084,7 +21084,7 @@
       </c>
       <c r="E826" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21109,7 +21109,7 @@
       </c>
       <c r="E827" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21134,7 +21134,7 @@
       </c>
       <c r="E828" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21159,7 +21159,7 @@
       </c>
       <c r="E829" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21184,7 +21184,7 @@
       </c>
       <c r="E830" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21209,7 +21209,7 @@
       </c>
       <c r="E831" s="3" t="inlineStr">
         <is>
-          <t>07-05-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21234,7 +21234,7 @@
       </c>
       <c r="E832" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21259,7 +21259,7 @@
       </c>
       <c r="E833" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21284,7 +21284,7 @@
       </c>
       <c r="E834" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21309,7 +21309,7 @@
       </c>
       <c r="E835" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21334,7 +21334,7 @@
       </c>
       <c r="E836" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21359,7 +21359,7 @@
       </c>
       <c r="E837" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21384,7 +21384,7 @@
       </c>
       <c r="E838" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21409,7 +21409,7 @@
       </c>
       <c r="E839" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21434,7 +21434,7 @@
       </c>
       <c r="E840" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21459,7 +21459,7 @@
       </c>
       <c r="E841" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21484,7 +21484,7 @@
       </c>
       <c r="E842" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21509,7 +21509,7 @@
       </c>
       <c r="E843" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21534,7 +21534,7 @@
       </c>
       <c r="E844" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21559,7 +21559,7 @@
       </c>
       <c r="E845" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21584,7 +21584,7 @@
       </c>
       <c r="E846" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21609,7 +21609,7 @@
       </c>
       <c r="E847" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21634,7 +21634,7 @@
       </c>
       <c r="E848" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21659,7 +21659,7 @@
       </c>
       <c r="E849" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21684,7 +21684,7 @@
       </c>
       <c r="E850" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="E851" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="E852" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21759,7 +21759,7 @@
       </c>
       <c r="E853" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21784,7 +21784,7 @@
       </c>
       <c r="E854" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21809,7 +21809,7 @@
       </c>
       <c r="E855" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21834,7 +21834,7 @@
       </c>
       <c r="E856" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21859,7 +21859,7 @@
       </c>
       <c r="E857" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21884,7 +21884,7 @@
       </c>
       <c r="E858" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21909,7 +21909,7 @@
       </c>
       <c r="E859" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21934,7 +21934,7 @@
       </c>
       <c r="E860" s="3" t="inlineStr">
         <is>
-          <t>07-05-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21959,7 +21959,7 @@
       </c>
       <c r="E861" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21984,7 +21984,7 @@
       </c>
       <c r="E862" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22009,7 +22009,7 @@
       </c>
       <c r="E863" s="3" t="inlineStr">
         <is>
-          <t>07-05-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22034,7 +22034,7 @@
       </c>
       <c r="E864" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22059,7 +22059,7 @@
       </c>
       <c r="E865" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22084,7 +22084,7 @@
       </c>
       <c r="E866" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22109,7 +22109,7 @@
       </c>
       <c r="E867" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22134,7 +22134,7 @@
       </c>
       <c r="E868" s="3" t="inlineStr">
         <is>
-          <t>07-05-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22159,7 +22159,7 @@
       </c>
       <c r="E869" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22184,7 +22184,7 @@
       </c>
       <c r="E870" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22209,7 +22209,7 @@
       </c>
       <c r="E871" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22234,7 +22234,7 @@
       </c>
       <c r="E872" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22259,7 +22259,7 @@
       </c>
       <c r="E873" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22284,7 +22284,7 @@
       </c>
       <c r="E874" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22309,7 +22309,7 @@
       </c>
       <c r="E875" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22334,7 +22334,7 @@
       </c>
       <c r="E876" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22359,7 +22359,7 @@
       </c>
       <c r="E877" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22384,7 +22384,7 @@
       </c>
       <c r="E878" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22409,7 +22409,7 @@
       </c>
       <c r="E879" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="E880" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22459,7 +22459,7 @@
       </c>
       <c r="E881" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22484,7 +22484,7 @@
       </c>
       <c r="E882" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22509,7 +22509,7 @@
       </c>
       <c r="E883" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22534,7 +22534,7 @@
       </c>
       <c r="E884" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22559,7 +22559,7 @@
       </c>
       <c r="E885" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22584,7 +22584,7 @@
       </c>
       <c r="E886" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22609,7 +22609,7 @@
       </c>
       <c r="E887" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22634,7 +22634,7 @@
       </c>
       <c r="E888" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22659,7 +22659,7 @@
       </c>
       <c r="E889" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22684,7 +22684,7 @@
       </c>
       <c r="E890" s="3" t="inlineStr">
         <is>
-          <t>26-02-21</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22709,7 +22709,7 @@
       </c>
       <c r="E891" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22734,7 +22734,7 @@
       </c>
       <c r="E892" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22759,7 +22759,7 @@
       </c>
       <c r="E893" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22784,7 +22784,7 @@
       </c>
       <c r="E894" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22809,7 +22809,7 @@
       </c>
       <c r="E895" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22834,7 +22834,7 @@
       </c>
       <c r="E896" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22859,7 +22859,7 @@
       </c>
       <c r="E897" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22884,7 +22884,7 @@
       </c>
       <c r="E898" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22909,7 +22909,7 @@
       </c>
       <c r="E899" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22934,7 +22934,7 @@
       </c>
       <c r="E900" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22959,7 +22959,7 @@
       </c>
       <c r="E901" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22984,7 +22984,7 @@
       </c>
       <c r="E902" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23009,7 +23009,7 @@
       </c>
       <c r="E903" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23034,7 +23034,7 @@
       </c>
       <c r="E904" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23059,7 +23059,7 @@
       </c>
       <c r="E905" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23084,7 +23084,7 @@
       </c>
       <c r="E906" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23109,7 +23109,7 @@
       </c>
       <c r="E907" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="E908" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23159,7 +23159,7 @@
       </c>
       <c r="E909" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23184,7 +23184,7 @@
       </c>
       <c r="E910" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23209,7 +23209,7 @@
       </c>
       <c r="E911" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23234,7 +23234,7 @@
       </c>
       <c r="E912" s="3" t="inlineStr">
         <is>
-          <t>07-05-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23259,7 +23259,7 @@
       </c>
       <c r="E913" s="3" t="inlineStr">
         <is>
-          <t>07-05-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23284,7 +23284,7 @@
       </c>
       <c r="E914" s="3" t="inlineStr">
         <is>
-          <t>07-05-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23309,7 +23309,7 @@
       </c>
       <c r="E915" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23334,7 +23334,7 @@
       </c>
       <c r="E916" s="3" t="inlineStr">
         <is>
-          <t>07-05-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23359,7 +23359,7 @@
       </c>
       <c r="E917" s="3" t="inlineStr">
         <is>
-          <t>07-05-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23384,7 +23384,7 @@
       </c>
       <c r="E918" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23409,7 +23409,7 @@
       </c>
       <c r="E919" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23434,7 +23434,7 @@
       </c>
       <c r="E920" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23459,7 +23459,7 @@
       </c>
       <c r="E921" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23484,7 +23484,7 @@
       </c>
       <c r="E922" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23509,7 +23509,7 @@
       </c>
       <c r="E923" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23534,7 +23534,7 @@
       </c>
       <c r="E924" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23559,7 +23559,7 @@
       </c>
       <c r="E925" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23584,7 +23584,7 @@
       </c>
       <c r="E926" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23609,7 +23609,7 @@
       </c>
       <c r="E927" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23634,7 +23634,7 @@
       </c>
       <c r="E928" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23659,7 +23659,7 @@
       </c>
       <c r="E929" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23684,7 +23684,7 @@
       </c>
       <c r="E930" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23709,7 +23709,7 @@
       </c>
       <c r="E931" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23734,7 +23734,7 @@
       </c>
       <c r="E932" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23759,7 +23759,7 @@
       </c>
       <c r="E933" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23784,7 +23784,7 @@
       </c>
       <c r="E934" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23809,7 +23809,7 @@
       </c>
       <c r="E935" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="E936" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23859,7 +23859,7 @@
       </c>
       <c r="E937" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23884,7 +23884,7 @@
       </c>
       <c r="E938" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23909,7 +23909,7 @@
       </c>
       <c r="E939" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23934,7 +23934,7 @@
       </c>
       <c r="E940" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23959,7 +23959,7 @@
       </c>
       <c r="E941" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23984,7 +23984,7 @@
       </c>
       <c r="E942" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24009,7 +24009,7 @@
       </c>
       <c r="E943" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24034,7 +24034,7 @@
       </c>
       <c r="E944" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24059,7 +24059,7 @@
       </c>
       <c r="E945" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24084,7 +24084,7 @@
       </c>
       <c r="E946" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="E947" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24134,7 +24134,7 @@
       </c>
       <c r="E948" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24159,7 +24159,7 @@
       </c>
       <c r="E949" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24184,7 +24184,7 @@
       </c>
       <c r="E950" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24209,7 +24209,7 @@
       </c>
       <c r="E951" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="E952" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24259,7 +24259,7 @@
       </c>
       <c r="E953" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24284,7 +24284,7 @@
       </c>
       <c r="E954" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24309,7 +24309,7 @@
       </c>
       <c r="E955" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24334,7 +24334,7 @@
       </c>
       <c r="E956" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24359,7 +24359,7 @@
       </c>
       <c r="E957" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24384,7 +24384,7 @@
       </c>
       <c r="E958" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24409,7 +24409,7 @@
       </c>
       <c r="E959" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24434,7 +24434,7 @@
       </c>
       <c r="E960" s="3" t="inlineStr">
         <is>
-          <t>27-06-25</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24459,7 +24459,7 @@
       </c>
       <c r="E961" s="3" t="inlineStr">
         <is>
-          <t>22-04-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24484,7 +24484,7 @@
       </c>
       <c r="E962" s="3" t="inlineStr">
         <is>
-          <t>22-04-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24509,7 +24509,7 @@
       </c>
       <c r="E963" s="3" t="inlineStr">
         <is>
-          <t>22-04-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="E964" s="3" t="inlineStr">
         <is>
-          <t>22-04-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24559,7 +24559,7 @@
       </c>
       <c r="E965" s="3" t="inlineStr">
         <is>
-          <t>22-04-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24584,7 +24584,7 @@
       </c>
       <c r="E966" s="3" t="inlineStr">
         <is>
-          <t>22-04-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24609,7 +24609,7 @@
       </c>
       <c r="E967" s="3" t="inlineStr">
         <is>
-          <t>22-04-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24634,7 +24634,7 @@
       </c>
       <c r="E968" s="3" t="inlineStr">
         <is>
-          <t>22-04-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24659,7 +24659,7 @@
       </c>
       <c r="E969" s="3" t="inlineStr">
         <is>
-          <t>22-04-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24684,7 +24684,7 @@
       </c>
       <c r="E970" s="3" t="inlineStr">
         <is>
-          <t>22-04-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24709,7 +24709,7 @@
       </c>
       <c r="E971" s="3" t="inlineStr">
         <is>
-          <t>22-04-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>

--- a/Critical Raw Materials List.xlsx
+++ b/Critical Raw Materials List.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4659,7 @@
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -5584,7 +5584,7 @@
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -5609,7 +5609,7 @@
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -6009,7 +6009,7 @@
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6084,7 @@
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="E241" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="E242" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="E243" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="E247" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="E248" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -6659,7 +6659,7 @@
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -6709,7 +6709,7 @@
       </c>
       <c r="E251" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="E253" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="E255" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -6859,7 +6859,7 @@
       </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="E259" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="E260" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -6959,7 +6959,7 @@
       </c>
       <c r="E261" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="E263" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="E264" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="E265" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -7084,7 +7084,7 @@
       </c>
       <c r="E266" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="E267" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="E268" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
       </c>
       <c r="E269" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
       </c>
       <c r="E270" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="E271" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="E272" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="E273" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="E274" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="E275" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="E276" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7359,7 @@
       </c>
       <c r="E277" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="E278" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -7409,7 +7409,7 @@
       </c>
       <c r="E279" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="E280" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="E281" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="E282" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -7509,7 +7509,7 @@
       </c>
       <c r="E283" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -7534,7 +7534,7 @@
       </c>
       <c r="E284" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -7584,7 +7584,7 @@
       </c>
       <c r="E286" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="E287" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="E288" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="E289" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="E290" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="E291" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="E292" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -7759,7 +7759,7 @@
       </c>
       <c r="E293" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -7784,7 +7784,7 @@
       </c>
       <c r="E294" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="E295" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="E296" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="E297" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="E298" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="E299" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="E300" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="E301" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="E302" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="E303" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="E304" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="E305" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="E306" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -8109,7 +8109,7 @@
       </c>
       <c r="E307" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="E308" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="E309" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="E310" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -8209,7 +8209,7 @@
       </c>
       <c r="E311" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="E312" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="E313" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="E314" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="E315" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="E316" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="E317" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="E318" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -8409,7 +8409,7 @@
       </c>
       <c r="E319" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="E320" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="E321" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="E322" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="E323" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="E324" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -8559,7 +8559,7 @@
       </c>
       <c r="E325" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -8584,7 +8584,7 @@
       </c>
       <c r="E326" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -8609,7 +8609,7 @@
       </c>
       <c r="E327" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="E328" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="E329" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -8684,7 +8684,7 @@
       </c>
       <c r="E330" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -8709,7 +8709,7 @@
       </c>
       <c r="E331" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -8734,7 +8734,7 @@
       </c>
       <c r="E332" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -8759,7 +8759,7 @@
       </c>
       <c r="E333" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="E334" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -8809,7 +8809,7 @@
       </c>
       <c r="E335" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="E336" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -8859,7 +8859,7 @@
       </c>
       <c r="E337" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -8884,7 +8884,7 @@
       </c>
       <c r="E338" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -8909,7 +8909,7 @@
       </c>
       <c r="E339" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="E340" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="E341" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -8984,7 +8984,7 @@
       </c>
       <c r="E342" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -9009,7 +9009,7 @@
       </c>
       <c r="E343" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="E344" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -9059,7 +9059,7 @@
       </c>
       <c r="E345" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -9084,7 +9084,7 @@
       </c>
       <c r="E346" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="E347" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="E348" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -9184,7 +9184,7 @@
       </c>
       <c r="E350" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -9209,7 +9209,7 @@
       </c>
       <c r="E351" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="E352" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -9259,7 +9259,7 @@
       </c>
       <c r="E353" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="E354" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -9309,7 +9309,7 @@
       </c>
       <c r="E355" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="E356" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="E357" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -9384,7 +9384,7 @@
       </c>
       <c r="E358" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -9409,7 +9409,7 @@
       </c>
       <c r="E359" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -9434,7 +9434,7 @@
       </c>
       <c r="E360" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -9459,7 +9459,7 @@
       </c>
       <c r="E361" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -9484,7 +9484,7 @@
       </c>
       <c r="E362" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="E363" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="E364" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -9559,7 +9559,7 @@
       </c>
       <c r="E365" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -9584,7 +9584,7 @@
       </c>
       <c r="E366" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="E367" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -9634,7 +9634,7 @@
       </c>
       <c r="E368" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -9659,7 +9659,7 @@
       </c>
       <c r="E369" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -9684,7 +9684,7 @@
       </c>
       <c r="E370" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="E371" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="E372" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="E373" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="E374" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="E375" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="E376" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -9859,7 +9859,7 @@
       </c>
       <c r="E377" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -9884,7 +9884,7 @@
       </c>
       <c r="E378" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -9909,7 +9909,7 @@
       </c>
       <c r="E379" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="E380" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
       </c>
       <c r="E381" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -9984,7 +9984,7 @@
       </c>
       <c r="E382" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="E383" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10034,7 +10034,7 @@
       </c>
       <c r="E384" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10059,7 +10059,7 @@
       </c>
       <c r="E385" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="E386" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10109,7 +10109,7 @@
       </c>
       <c r="E387" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10134,7 +10134,7 @@
       </c>
       <c r="E388" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10159,7 +10159,7 @@
       </c>
       <c r="E389" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10184,7 +10184,7 @@
       </c>
       <c r="E390" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="E391" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10234,7 +10234,7 @@
       </c>
       <c r="E392" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="E393" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10284,7 +10284,7 @@
       </c>
       <c r="E394" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10309,7 +10309,7 @@
       </c>
       <c r="E395" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="E396" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10359,7 +10359,7 @@
       </c>
       <c r="E397" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="E398" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10409,7 +10409,7 @@
       </c>
       <c r="E399" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="E400" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10459,7 +10459,7 @@
       </c>
       <c r="E401" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10484,7 +10484,7 @@
       </c>
       <c r="E402" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10509,7 +10509,7 @@
       </c>
       <c r="E403" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="E404" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10559,7 +10559,7 @@
       </c>
       <c r="E405" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="E406" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10609,7 +10609,7 @@
       </c>
       <c r="E407" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="E408" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10659,7 +10659,7 @@
       </c>
       <c r="E409" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10684,7 +10684,7 @@
       </c>
       <c r="E410" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10709,7 +10709,7 @@
       </c>
       <c r="E411" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10734,7 +10734,7 @@
       </c>
       <c r="E412" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10759,7 +10759,7 @@
       </c>
       <c r="E413" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10784,7 +10784,7 @@
       </c>
       <c r="E414" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10809,7 +10809,7 @@
       </c>
       <c r="E415" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10834,7 +10834,7 @@
       </c>
       <c r="E416" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="E417" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10884,7 +10884,7 @@
       </c>
       <c r="E418" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="E419" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="E420" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10959,7 +10959,7 @@
       </c>
       <c r="E421" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -10984,7 +10984,7 @@
       </c>
       <c r="E422" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="E423" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="E424" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11059,7 +11059,7 @@
       </c>
       <c r="E425" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11084,7 +11084,7 @@
       </c>
       <c r="E426" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11109,7 +11109,7 @@
       </c>
       <c r="E427" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11134,7 +11134,7 @@
       </c>
       <c r="E428" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11159,7 +11159,7 @@
       </c>
       <c r="E429" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11184,7 +11184,7 @@
       </c>
       <c r="E430" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11209,7 +11209,7 @@
       </c>
       <c r="E431" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="E432" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11259,7 @@
       </c>
       <c r="E433" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11284,7 +11284,7 @@
       </c>
       <c r="E434" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11309,7 +11309,7 @@
       </c>
       <c r="E435" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11334,7 +11334,7 @@
       </c>
       <c r="E436" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="E437" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11384,7 +11384,7 @@
       </c>
       <c r="E438" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11409,7 +11409,7 @@
       </c>
       <c r="E439" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11434,7 +11434,7 @@
       </c>
       <c r="E440" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11459,7 +11459,7 @@
       </c>
       <c r="E441" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11484,7 +11484,7 @@
       </c>
       <c r="E442" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11509,7 +11509,7 @@
       </c>
       <c r="E443" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11534,7 +11534,7 @@
       </c>
       <c r="E444" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11559,7 +11559,7 @@
       </c>
       <c r="E445" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11584,7 +11584,7 @@
       </c>
       <c r="E446" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="E447" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11634,7 +11634,7 @@
       </c>
       <c r="E448" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="E449" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11684,7 +11684,7 @@
       </c>
       <c r="E450" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="E451" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="E452" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11759,7 +11759,7 @@
       </c>
       <c r="E453" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="E454" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="E455" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11834,7 +11834,7 @@
       </c>
       <c r="E456" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="E457" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="E458" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11909,7 +11909,7 @@
       </c>
       <c r="E459" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="E460" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11959,7 +11959,7 @@
       </c>
       <c r="E461" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -11984,7 +11984,7 @@
       </c>
       <c r="E462" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12009,7 +12009,7 @@
       </c>
       <c r="E463" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="E464" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12059,7 +12059,7 @@
       </c>
       <c r="E465" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12084,7 +12084,7 @@
       </c>
       <c r="E466" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12109,7 +12109,7 @@
       </c>
       <c r="E467" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12134,7 +12134,7 @@
       </c>
       <c r="E468" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12159,7 +12159,7 @@
       </c>
       <c r="E469" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12184,7 +12184,7 @@
       </c>
       <c r="E470" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12209,7 +12209,7 @@
       </c>
       <c r="E471" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12234,7 +12234,7 @@
       </c>
       <c r="E472" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12259,7 +12259,7 @@
       </c>
       <c r="E473" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12284,7 +12284,7 @@
       </c>
       <c r="E474" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12309,7 +12309,7 @@
       </c>
       <c r="E475" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12334,7 +12334,7 @@
       </c>
       <c r="E476" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12359,7 +12359,7 @@
       </c>
       <c r="E477" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12384,7 +12384,7 @@
       </c>
       <c r="E478" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12409,7 +12409,7 @@
       </c>
       <c r="E479" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12434,7 +12434,7 @@
       </c>
       <c r="E480" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="E481" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12484,7 +12484,7 @@
       </c>
       <c r="E482" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12509,7 +12509,7 @@
       </c>
       <c r="E483" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12534,7 @@
       </c>
       <c r="E484" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="E485" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12584,7 +12584,7 @@
       </c>
       <c r="E486" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12609,7 +12609,7 @@
       </c>
       <c r="E487" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="E488" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="E489" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12684,7 +12684,7 @@
       </c>
       <c r="E490" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12709,7 +12709,7 @@
       </c>
       <c r="E491" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12734,7 +12734,7 @@
       </c>
       <c r="E492" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="E493" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12784,7 +12784,7 @@
       </c>
       <c r="E494" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12809,7 +12809,7 @@
       </c>
       <c r="E495" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12834,7 +12834,7 @@
       </c>
       <c r="E496" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="E497" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="E498" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12909,7 +12909,7 @@
       </c>
       <c r="E499" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12934,7 +12934,7 @@
       </c>
       <c r="E500" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12959,7 +12959,7 @@
       </c>
       <c r="E501" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -12984,7 +12984,7 @@
       </c>
       <c r="E502" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13009,7 +13009,7 @@
       </c>
       <c r="E503" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13034,7 +13034,7 @@
       </c>
       <c r="E504" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13059,7 +13059,7 @@
       </c>
       <c r="E505" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13084,7 +13084,7 @@
       </c>
       <c r="E506" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13109,7 +13109,7 @@
       </c>
       <c r="E507" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13134,7 +13134,7 @@
       </c>
       <c r="E508" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13159,7 +13159,7 @@
       </c>
       <c r="E509" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="E510" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13209,7 +13209,7 @@
       </c>
       <c r="E511" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13234,7 +13234,7 @@
       </c>
       <c r="E512" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13259,7 +13259,7 @@
       </c>
       <c r="E513" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13284,7 +13284,7 @@
       </c>
       <c r="E514" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13309,7 +13309,7 @@
       </c>
       <c r="E515" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="E516" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13359,7 +13359,7 @@
       </c>
       <c r="E517" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13384,7 +13384,7 @@
       </c>
       <c r="E518" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13409,7 +13409,7 @@
       </c>
       <c r="E519" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13434,7 +13434,7 @@
       </c>
       <c r="E520" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13459,7 +13459,7 @@
       </c>
       <c r="E521" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13484,7 +13484,7 @@
       </c>
       <c r="E522" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="E523" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13534,7 +13534,7 @@
       </c>
       <c r="E524" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13559,7 +13559,7 @@
       </c>
       <c r="E525" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13584,7 +13584,7 @@
       </c>
       <c r="E526" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13609,7 +13609,7 @@
       </c>
       <c r="E527" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="E528" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13659,7 +13659,7 @@
       </c>
       <c r="E529" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13684,7 +13684,7 @@
       </c>
       <c r="E530" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13709,7 +13709,7 @@
       </c>
       <c r="E531" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13734,7 +13734,7 @@
       </c>
       <c r="E532" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13759,7 +13759,7 @@
       </c>
       <c r="E533" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13784,7 +13784,7 @@
       </c>
       <c r="E534" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13809,7 +13809,7 @@
       </c>
       <c r="E535" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13834,7 +13834,7 @@
       </c>
       <c r="E536" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13859,7 +13859,7 @@
       </c>
       <c r="E537" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13884,7 +13884,7 @@
       </c>
       <c r="E538" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13909,7 +13909,7 @@
       </c>
       <c r="E539" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13934,7 +13934,7 @@
       </c>
       <c r="E540" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13959,7 +13959,7 @@
       </c>
       <c r="E541" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -13984,7 +13984,7 @@
       </c>
       <c r="E542" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14009,7 +14009,7 @@
       </c>
       <c r="E543" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="E544" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14059,7 +14059,7 @@
       </c>
       <c r="E545" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14084,7 +14084,7 @@
       </c>
       <c r="E546" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="E547" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14134,7 +14134,7 @@
       </c>
       <c r="E548" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="E549" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14184,7 +14184,7 @@
       </c>
       <c r="E550" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14209,7 +14209,7 @@
       </c>
       <c r="E551" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14234,7 +14234,7 @@
       </c>
       <c r="E552" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14259,7 +14259,7 @@
       </c>
       <c r="E553" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="E554" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14309,7 +14309,7 @@
       </c>
       <c r="E555" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14334,7 +14334,7 @@
       </c>
       <c r="E556" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14359,7 +14359,7 @@
       </c>
       <c r="E557" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14384,7 +14384,7 @@
       </c>
       <c r="E558" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14409,7 @@
       </c>
       <c r="E559" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14434,7 +14434,7 @@
       </c>
       <c r="E560" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14459,7 +14459,7 @@
       </c>
       <c r="E561" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="E562" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14509,7 +14509,7 @@
       </c>
       <c r="E563" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="E564" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14559,7 +14559,7 @@
       </c>
       <c r="E565" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14584,7 +14584,7 @@
       </c>
       <c r="E566" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14609,7 +14609,7 @@
       </c>
       <c r="E567" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14634,7 +14634,7 @@
       </c>
       <c r="E568" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14659,7 +14659,7 @@
       </c>
       <c r="E569" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14684,7 +14684,7 @@
       </c>
       <c r="E570" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14709,7 +14709,7 @@
       </c>
       <c r="E571" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="E572" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14759,7 +14759,7 @@
       </c>
       <c r="E573" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="E574" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="E575" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="E576" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14859,7 +14859,7 @@
       </c>
       <c r="E577" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14884,7 +14884,7 @@
       </c>
       <c r="E578" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14909,7 +14909,7 @@
       </c>
       <c r="E579" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14934,7 +14934,7 @@
       </c>
       <c r="E580" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14959,7 +14959,7 @@
       </c>
       <c r="E581" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="E582" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15009,7 +15009,7 @@
       </c>
       <c r="E583" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15034,7 +15034,7 @@
       </c>
       <c r="E584" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15059,7 +15059,7 @@
       </c>
       <c r="E585" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15084,7 +15084,7 @@
       </c>
       <c r="E586" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15109,7 +15109,7 @@
       </c>
       <c r="E587" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="E588" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15159,7 +15159,7 @@
       </c>
       <c r="E589" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15184,7 +15184,7 @@
       </c>
       <c r="E590" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15209,7 +15209,7 @@
       </c>
       <c r="E591" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15234,7 +15234,7 @@
       </c>
       <c r="E592" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15259,7 +15259,7 @@
       </c>
       <c r="E593" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15284,7 +15284,7 @@
       </c>
       <c r="E594" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15309,7 +15309,7 @@
       </c>
       <c r="E595" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15334,7 +15334,7 @@
       </c>
       <c r="E596" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15359,7 +15359,7 @@
       </c>
       <c r="E597" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15384,7 +15384,7 @@
       </c>
       <c r="E598" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="E599" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="E600" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15459,7 @@
       </c>
       <c r="E601" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="E602" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15509,7 +15509,7 @@
       </c>
       <c r="E603" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15534,7 +15534,7 @@
       </c>
       <c r="E604" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15559,7 +15559,7 @@
       </c>
       <c r="E605" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15584,7 +15584,7 @@
       </c>
       <c r="E606" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15609,7 +15609,7 @@
       </c>
       <c r="E607" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15634,7 +15634,7 @@
       </c>
       <c r="E608" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15659,7 +15659,7 @@
       </c>
       <c r="E609" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15684,7 +15684,7 @@
       </c>
       <c r="E610" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15709,7 +15709,7 @@
       </c>
       <c r="E611" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="E612" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15759,7 +15759,7 @@
       </c>
       <c r="E613" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15784,7 +15784,7 @@
       </c>
       <c r="E614" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15809,7 +15809,7 @@
       </c>
       <c r="E615" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15834,7 +15834,7 @@
       </c>
       <c r="E616" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15859,7 +15859,7 @@
       </c>
       <c r="E617" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="E618" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15909,7 +15909,7 @@
       </c>
       <c r="E619" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15934,7 +15934,7 @@
       </c>
       <c r="E620" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15959,7 +15959,7 @@
       </c>
       <c r="E621" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="E622" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16009,7 +16009,7 @@
       </c>
       <c r="E623" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16034,7 +16034,7 @@
       </c>
       <c r="E624" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16059,7 +16059,7 @@
       </c>
       <c r="E625" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16084,7 +16084,7 @@
       </c>
       <c r="E626" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16109,7 +16109,7 @@
       </c>
       <c r="E627" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="E628" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="E629" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16184,7 +16184,7 @@
       </c>
       <c r="E630" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16209,7 +16209,7 @@
       </c>
       <c r="E631" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16234,7 +16234,7 @@
       </c>
       <c r="E632" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16259,7 +16259,7 @@
       </c>
       <c r="E633" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16284,7 +16284,7 @@
       </c>
       <c r="E634" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16309,7 +16309,7 @@
       </c>
       <c r="E635" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16334,7 +16334,7 @@
       </c>
       <c r="E636" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16359,7 +16359,7 @@
       </c>
       <c r="E637" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16384,7 +16384,7 @@
       </c>
       <c r="E638" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16409,7 +16409,7 @@
       </c>
       <c r="E639" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="E640" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16459,7 +16459,7 @@
       </c>
       <c r="E641" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16484,7 +16484,7 @@
       </c>
       <c r="E642" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16509,7 +16509,7 @@
       </c>
       <c r="E643" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16534,7 +16534,7 @@
       </c>
       <c r="E644" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="E645" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16584,7 +16584,7 @@
       </c>
       <c r="E646" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16609,7 +16609,7 @@
       </c>
       <c r="E647" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="E648" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16659,7 +16659,7 @@
       </c>
       <c r="E649" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16684,7 +16684,7 @@
       </c>
       <c r="E650" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16709,7 +16709,7 @@
       </c>
       <c r="E651" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16734,7 +16734,7 @@
       </c>
       <c r="E652" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16759,7 +16759,7 @@
       </c>
       <c r="E653" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="E654" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="E655" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="E656" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16859,7 +16859,7 @@
       </c>
       <c r="E657" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16884,7 +16884,7 @@
       </c>
       <c r="E658" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16909,7 +16909,7 @@
       </c>
       <c r="E659" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16934,7 +16934,7 @@
       </c>
       <c r="E660" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16959,7 +16959,7 @@
       </c>
       <c r="E661" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -16984,7 +16984,7 @@
       </c>
       <c r="E662" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17009,7 +17009,7 @@
       </c>
       <c r="E663" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17034,7 +17034,7 @@
       </c>
       <c r="E664" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17059,7 +17059,7 @@
       </c>
       <c r="E665" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17084,7 +17084,7 @@
       </c>
       <c r="E666" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17109,7 +17109,7 @@
       </c>
       <c r="E667" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17134,7 +17134,7 @@
       </c>
       <c r="E668" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17159,7 +17159,7 @@
       </c>
       <c r="E669" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="E670" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17209,7 +17209,7 @@
       </c>
       <c r="E671" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17234,7 +17234,7 @@
       </c>
       <c r="E672" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17259,7 +17259,7 @@
       </c>
       <c r="E673" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17284,7 +17284,7 @@
       </c>
       <c r="E674" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17309,7 +17309,7 @@
       </c>
       <c r="E675" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17334,7 +17334,7 @@
       </c>
       <c r="E676" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17359,7 +17359,7 @@
       </c>
       <c r="E677" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17384,7 +17384,7 @@
       </c>
       <c r="E678" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="E679" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17434,7 +17434,7 @@
       </c>
       <c r="E680" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17459,7 +17459,7 @@
       </c>
       <c r="E681" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="E682" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17509,7 +17509,7 @@
       </c>
       <c r="E683" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="E684" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17559,7 +17559,7 @@
       </c>
       <c r="E685" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17584,7 +17584,7 @@
       </c>
       <c r="E686" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17609,7 +17609,7 @@
       </c>
       <c r="E687" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="E688" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17659,7 +17659,7 @@
       </c>
       <c r="E689" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17684,7 +17684,7 @@
       </c>
       <c r="E690" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17709,7 +17709,7 @@
       </c>
       <c r="E691" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17734,7 +17734,7 @@
       </c>
       <c r="E692" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="E693" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17784,7 +17784,7 @@
       </c>
       <c r="E694" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17809,7 +17809,7 @@
       </c>
       <c r="E695" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17834,7 +17834,7 @@
       </c>
       <c r="E696" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17859,7 +17859,7 @@
       </c>
       <c r="E697" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17884,7 +17884,7 @@
       </c>
       <c r="E698" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17909,7 +17909,7 @@
       </c>
       <c r="E699" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17934,7 +17934,7 @@
       </c>
       <c r="E700" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17959,7 +17959,7 @@
       </c>
       <c r="E701" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -17984,7 +17984,7 @@
       </c>
       <c r="E702" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18009,7 +18009,7 @@
       </c>
       <c r="E703" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18034,7 +18034,7 @@
       </c>
       <c r="E704" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18059,7 +18059,7 @@
       </c>
       <c r="E705" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18084,7 +18084,7 @@
       </c>
       <c r="E706" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18109,7 +18109,7 @@
       </c>
       <c r="E707" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18134,7 +18134,7 @@
       </c>
       <c r="E708" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18159,7 +18159,7 @@
       </c>
       <c r="E709" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18184,7 +18184,7 @@
       </c>
       <c r="E710" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18209,7 +18209,7 @@
       </c>
       <c r="E711" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="E712" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18259,7 +18259,7 @@
       </c>
       <c r="E713" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18284,7 +18284,7 @@
       </c>
       <c r="E714" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18309,7 +18309,7 @@
       </c>
       <c r="E715" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18334,7 +18334,7 @@
       </c>
       <c r="E716" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18359,7 +18359,7 @@
       </c>
       <c r="E717" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18384,7 +18384,7 @@
       </c>
       <c r="E718" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18409,7 +18409,7 @@
       </c>
       <c r="E719" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18434,7 +18434,7 @@
       </c>
       <c r="E720" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18459,7 +18459,7 @@
       </c>
       <c r="E721" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18484,7 +18484,7 @@
       </c>
       <c r="E722" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18509,7 +18509,7 @@
       </c>
       <c r="E723" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18534,7 +18534,7 @@
       </c>
       <c r="E724" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18559,7 +18559,7 @@
       </c>
       <c r="E725" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18584,7 +18584,7 @@
       </c>
       <c r="E726" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18609,7 +18609,7 @@
       </c>
       <c r="E727" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18634,7 +18634,7 @@
       </c>
       <c r="E728" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18659,7 +18659,7 @@
       </c>
       <c r="E729" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18684,7 +18684,7 @@
       </c>
       <c r="E730" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="E731" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18734,7 +18734,7 @@
       </c>
       <c r="E732" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18759,7 +18759,7 @@
       </c>
       <c r="E733" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18784,7 +18784,7 @@
       </c>
       <c r="E734" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="E735" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18834,7 +18834,7 @@
       </c>
       <c r="E736" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18859,7 +18859,7 @@
       </c>
       <c r="E737" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18884,7 +18884,7 @@
       </c>
       <c r="E738" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18909,7 +18909,7 @@
       </c>
       <c r="E739" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="E740" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18959,7 +18959,7 @@
       </c>
       <c r="E741" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -18984,7 +18984,7 @@
       </c>
       <c r="E742" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19009,7 +19009,7 @@
       </c>
       <c r="E743" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="E744" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19059,7 +19059,7 @@
       </c>
       <c r="E745" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19084,7 +19084,7 @@
       </c>
       <c r="E746" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19109,7 +19109,7 @@
       </c>
       <c r="E747" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19134,7 +19134,7 @@
       </c>
       <c r="E748" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19159,7 +19159,7 @@
       </c>
       <c r="E749" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19184,7 +19184,7 @@
       </c>
       <c r="E750" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="E751" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19234,7 +19234,7 @@
       </c>
       <c r="E752" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19259,7 +19259,7 @@
       </c>
       <c r="E753" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19284,7 +19284,7 @@
       </c>
       <c r="E754" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19309,7 +19309,7 @@
       </c>
       <c r="E755" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19334,7 +19334,7 @@
       </c>
       <c r="E756" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="E757" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19384,7 +19384,7 @@
       </c>
       <c r="E758" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19409,7 +19409,7 @@
       </c>
       <c r="E759" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19434,7 +19434,7 @@
       </c>
       <c r="E760" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19459,7 +19459,7 @@
       </c>
       <c r="E761" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19484,7 +19484,7 @@
       </c>
       <c r="E762" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19509,7 +19509,7 @@
       </c>
       <c r="E763" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19534,7 +19534,7 @@
       </c>
       <c r="E764" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="E765" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19584,7 +19584,7 @@
       </c>
       <c r="E766" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19609,7 +19609,7 @@
       </c>
       <c r="E767" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="E768" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19659,7 +19659,7 @@
       </c>
       <c r="E769" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="E770" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19709,7 +19709,7 @@
       </c>
       <c r="E771" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19734,7 +19734,7 @@
       </c>
       <c r="E772" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="E773" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19784,7 +19784,7 @@
       </c>
       <c r="E774" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19809,7 +19809,7 @@
       </c>
       <c r="E775" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19834,7 +19834,7 @@
       </c>
       <c r="E776" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19859,7 +19859,7 @@
       </c>
       <c r="E777" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="E778" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19909,7 +19909,7 @@
       </c>
       <c r="E779" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19934,7 +19934,7 @@
       </c>
       <c r="E780" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19959,7 +19959,7 @@
       </c>
       <c r="E781" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -19984,7 +19984,7 @@
       </c>
       <c r="E782" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -20009,7 +20009,7 @@
       </c>
       <c r="E783" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -20034,7 +20034,7 @@
       </c>
       <c r="E784" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="E785" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -20084,7 +20084,7 @@
       </c>
       <c r="E786" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -20109,7 +20109,7 @@
       </c>
       <c r="E787" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -20134,7 +20134,7 @@
       </c>
       <c r="E788" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -20159,7 +20159,7 @@
       </c>
       <c r="E789" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -20184,7 +20184,7 @@
       </c>
       <c r="E790" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -20209,7 +20209,7 @@
       </c>
       <c r="E791" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -20234,7 +20234,7 @@
       </c>
       <c r="E792" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -20259,7 +20259,7 @@
       </c>
       <c r="E793" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -20284,7 +20284,7 @@
       </c>
       <c r="E794" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -20309,7 +20309,7 @@
       </c>
       <c r="E795" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="E796" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -20359,7 +20359,7 @@
       </c>
       <c r="E797" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="E798" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -20409,7 +20409,7 @@
       </c>
       <c r="E799" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -20434,7 +20434,7 @@
       </c>
       <c r="E800" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -20459,7 +20459,7 @@
       </c>
       <c r="E801" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -20484,7 +20484,7 @@
       </c>
       <c r="E802" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -20509,7 +20509,7 @@
       </c>
       <c r="E803" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -20534,7 +20534,7 @@
       </c>
       <c r="E804" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -20559,7 +20559,7 @@
       </c>
       <c r="E805" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -20584,7 +20584,7 @@
       </c>
       <c r="E806" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -20609,7 +20609,7 @@
       </c>
       <c r="E807" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -20634,7 +20634,7 @@
       </c>
       <c r="E808" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="E809" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -20684,7 +20684,7 @@
       </c>
       <c r="E810" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -20709,7 +20709,7 @@
       </c>
       <c r="E811" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="E812" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -20759,7 +20759,7 @@
       </c>
       <c r="E813" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -20784,7 +20784,7 @@
       </c>
       <c r="E814" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -20809,7 +20809,7 @@
       </c>
       <c r="E815" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="E816" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -20859,7 +20859,7 @@
       </c>
       <c r="E817" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -20884,7 +20884,7 @@
       </c>
       <c r="E818" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -20909,7 +20909,7 @@
       </c>
       <c r="E819" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -20934,7 +20934,7 @@
       </c>
       <c r="E820" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -20959,7 +20959,7 @@
       </c>
       <c r="E821" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -20984,7 +20984,7 @@
       </c>
       <c r="E822" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21009,7 +21009,7 @@
       </c>
       <c r="E823" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="E824" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21059,7 +21059,7 @@
       </c>
       <c r="E825" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21084,7 +21084,7 @@
       </c>
       <c r="E826" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21109,7 +21109,7 @@
       </c>
       <c r="E827" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21134,7 +21134,7 @@
       </c>
       <c r="E828" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21159,7 +21159,7 @@
       </c>
       <c r="E829" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21184,7 +21184,7 @@
       </c>
       <c r="E830" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21234,7 +21234,7 @@
       </c>
       <c r="E832" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21259,7 +21259,7 @@
       </c>
       <c r="E833" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21284,7 +21284,7 @@
       </c>
       <c r="E834" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21309,7 +21309,7 @@
       </c>
       <c r="E835" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21334,7 +21334,7 @@
       </c>
       <c r="E836" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21359,7 +21359,7 @@
       </c>
       <c r="E837" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21384,7 +21384,7 @@
       </c>
       <c r="E838" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21409,7 +21409,7 @@
       </c>
       <c r="E839" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21434,7 +21434,7 @@
       </c>
       <c r="E840" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21459,7 +21459,7 @@
       </c>
       <c r="E841" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21484,7 +21484,7 @@
       </c>
       <c r="E842" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21509,7 +21509,7 @@
       </c>
       <c r="E843" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21534,7 +21534,7 @@
       </c>
       <c r="E844" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -21559,7 +21559,7 @@
       </c>
       <c r="E845" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21584,7 +21584,7 @@
       </c>
       <c r="E846" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21609,7 +21609,7 @@
       </c>
       <c r="E847" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21634,7 +21634,7 @@
       </c>
       <c r="E848" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21659,7 +21659,7 @@
       </c>
       <c r="E849" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21684,7 +21684,7 @@
       </c>
       <c r="E850" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="E851" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="E852" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21759,7 +21759,7 @@
       </c>
       <c r="E853" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21784,7 +21784,7 @@
       </c>
       <c r="E854" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21809,7 +21809,7 @@
       </c>
       <c r="E855" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21834,7 +21834,7 @@
       </c>
       <c r="E856" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21859,7 +21859,7 @@
       </c>
       <c r="E857" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21884,7 +21884,7 @@
       </c>
       <c r="E858" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21909,7 +21909,7 @@
       </c>
       <c r="E859" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21959,7 +21959,7 @@
       </c>
       <c r="E861" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -21984,7 +21984,7 @@
       </c>
       <c r="E862" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -22034,7 +22034,7 @@
       </c>
       <c r="E864" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -22059,7 +22059,7 @@
       </c>
       <c r="E865" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -22084,7 +22084,7 @@
       </c>
       <c r="E866" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -22109,7 +22109,7 @@
       </c>
       <c r="E867" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -22159,7 +22159,7 @@
       </c>
       <c r="E869" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -22184,7 +22184,7 @@
       </c>
       <c r="E870" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -22209,7 +22209,7 @@
       </c>
       <c r="E871" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -22234,7 +22234,7 @@
       </c>
       <c r="E872" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -22259,7 +22259,7 @@
       </c>
       <c r="E873" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -22284,7 +22284,7 @@
       </c>
       <c r="E874" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -22309,7 +22309,7 @@
       </c>
       <c r="E875" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -22334,7 +22334,7 @@
       </c>
       <c r="E876" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -22359,7 +22359,7 @@
       </c>
       <c r="E877" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -22384,7 +22384,7 @@
       </c>
       <c r="E878" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -22409,7 +22409,7 @@
       </c>
       <c r="E879" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="E880" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -22459,7 +22459,7 @@
       </c>
       <c r="E881" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -22484,7 +22484,7 @@
       </c>
       <c r="E882" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -22509,7 +22509,7 @@
       </c>
       <c r="E883" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -22534,7 +22534,7 @@
       </c>
       <c r="E884" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -22559,7 +22559,7 @@
       </c>
       <c r="E885" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -22584,7 +22584,7 @@
       </c>
       <c r="E886" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -22609,7 +22609,7 @@
       </c>
       <c r="E887" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -22634,7 +22634,7 @@
       </c>
       <c r="E888" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -22659,7 +22659,7 @@
       </c>
       <c r="E889" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -22684,7 +22684,7 @@
       </c>
       <c r="E890" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>21-02-26</t>
         </is>
       </c>
     </row>
@@ -22709,7 +22709,7 @@
       </c>
       <c r="E891" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -22734,7 +22734,7 @@
       </c>
       <c r="E892" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -22759,7 +22759,7 @@
       </c>
       <c r="E893" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -22784,7 +22784,7 @@
       </c>
       <c r="E894" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -22809,7 +22809,7 @@
       </c>
       <c r="E895" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -22834,7 +22834,7 @@
       </c>
       <c r="E896" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -22859,7 +22859,7 @@
       </c>
       <c r="E897" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -22884,7 +22884,7 @@
       </c>
       <c r="E898" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -22909,7 +22909,7 @@
       </c>
       <c r="E899" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -22934,7 +22934,7 @@
       </c>
       <c r="E900" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -22959,7 +22959,7 @@
       </c>
       <c r="E901" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -22984,7 +22984,7 @@
       </c>
       <c r="E902" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23009,7 +23009,7 @@
       </c>
       <c r="E903" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23034,7 +23034,7 @@
       </c>
       <c r="E904" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23059,7 +23059,7 @@
       </c>
       <c r="E905" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23084,7 +23084,7 @@
       </c>
       <c r="E906" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23109,7 +23109,7 @@
       </c>
       <c r="E907" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="E908" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23159,7 +23159,7 @@
       </c>
       <c r="E909" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23184,7 +23184,7 @@
       </c>
       <c r="E910" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23209,7 +23209,7 @@
       </c>
       <c r="E911" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23309,7 +23309,7 @@
       </c>
       <c r="E915" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23384,7 +23384,7 @@
       </c>
       <c r="E918" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23409,7 +23409,7 @@
       </c>
       <c r="E919" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23434,7 +23434,7 @@
       </c>
       <c r="E920" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23459,7 +23459,7 @@
       </c>
       <c r="E921" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23484,7 +23484,7 @@
       </c>
       <c r="E922" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23509,7 +23509,7 @@
       </c>
       <c r="E923" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23534,7 +23534,7 @@
       </c>
       <c r="E924" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23559,7 +23559,7 @@
       </c>
       <c r="E925" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23584,7 +23584,7 @@
       </c>
       <c r="E926" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23609,7 +23609,7 @@
       </c>
       <c r="E927" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23634,7 +23634,7 @@
       </c>
       <c r="E928" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23659,7 +23659,7 @@
       </c>
       <c r="E929" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23684,7 +23684,7 @@
       </c>
       <c r="E930" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23709,7 +23709,7 @@
       </c>
       <c r="E931" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23734,7 +23734,7 @@
       </c>
       <c r="E932" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23759,7 +23759,7 @@
       </c>
       <c r="E933" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23784,7 +23784,7 @@
       </c>
       <c r="E934" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23809,7 +23809,7 @@
       </c>
       <c r="E935" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="E936" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23859,7 +23859,7 @@
       </c>
       <c r="E937" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23884,7 +23884,7 @@
       </c>
       <c r="E938" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23909,7 +23909,7 @@
       </c>
       <c r="E939" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23934,7 +23934,7 @@
       </c>
       <c r="E940" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23959,7 +23959,7 @@
       </c>
       <c r="E941" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -23984,7 +23984,7 @@
       </c>
       <c r="E942" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -24009,7 +24009,7 @@
       </c>
       <c r="E943" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -24034,7 +24034,7 @@
       </c>
       <c r="E944" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -24059,7 +24059,7 @@
       </c>
       <c r="E945" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -24084,7 +24084,7 @@
       </c>
       <c r="E946" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="E947" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -24134,7 +24134,7 @@
       </c>
       <c r="E948" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -24159,7 +24159,7 @@
       </c>
       <c r="E949" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -24184,7 +24184,7 @@
       </c>
       <c r="E950" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -24209,7 +24209,7 @@
       </c>
       <c r="E951" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="E952" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -24259,7 +24259,7 @@
       </c>
       <c r="E953" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -24284,7 +24284,7 @@
       </c>
       <c r="E954" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -24309,7 +24309,7 @@
       </c>
       <c r="E955" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -24334,7 +24334,7 @@
       </c>
       <c r="E956" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -24359,7 +24359,7 @@
       </c>
       <c r="E957" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -24384,7 +24384,7 @@
       </c>
       <c r="E958" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -24409,7 +24409,7 @@
       </c>
       <c r="E959" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -24434,7 +24434,7 @@
       </c>
       <c r="E960" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>25-06-27</t>
         </is>
       </c>
     </row>
@@ -24459,7 +24459,7 @@
       </c>
       <c r="E961" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>26-04-22</t>
         </is>
       </c>
     </row>
@@ -24484,7 +24484,7 @@
       </c>
       <c r="E962" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>26-04-22</t>
         </is>
       </c>
     </row>
@@ -24509,7 +24509,7 @@
       </c>
       <c r="E963" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>26-04-22</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="E964" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>26-04-22</t>
         </is>
       </c>
     </row>
@@ -24559,7 +24559,7 @@
       </c>
       <c r="E965" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>26-04-22</t>
         </is>
       </c>
     </row>
@@ -24584,7 +24584,7 @@
       </c>
       <c r="E966" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>26-04-22</t>
         </is>
       </c>
     </row>
@@ -24609,7 +24609,7 @@
       </c>
       <c r="E967" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>26-04-22</t>
         </is>
       </c>
     </row>
@@ -24634,7 +24634,7 @@
       </c>
       <c r="E968" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>26-04-22</t>
         </is>
       </c>
     </row>
@@ -24659,7 +24659,7 @@
       </c>
       <c r="E969" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>26-04-22</t>
         </is>
       </c>
     </row>
@@ -24684,7 +24684,7 @@
       </c>
       <c r="E970" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>26-04-22</t>
         </is>
       </c>
     </row>
@@ -24709,7 +24709,7 @@
       </c>
       <c r="E971" s="3" t="inlineStr">
         <is>
-          <t>26-05-07</t>
+          <t>26-04-22</t>
         </is>
       </c>
     </row>

--- a/Critical Raw Materials List.xlsx
+++ b/Critical Raw Materials List.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4659,7 @@
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5584,7 +5584,7 @@
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5609,7 +5609,7 @@
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6009,7 +6009,7 @@
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6084,7 @@
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="E241" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="E242" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="E243" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="E247" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="E248" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6659,7 +6659,7 @@
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6709,7 +6709,7 @@
       </c>
       <c r="E251" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="E253" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="E255" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6859,7 +6859,7 @@
       </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="E259" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="E260" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6959,7 +6959,7 @@
       </c>
       <c r="E261" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="E263" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="E264" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="E265" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7084,7 +7084,7 @@
       </c>
       <c r="E266" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="E267" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="E268" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
       </c>
       <c r="E269" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
       </c>
       <c r="E270" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="E271" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="E272" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="E273" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="E274" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="E275" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="E276" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7359,7 @@
       </c>
       <c r="E277" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="E278" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7409,7 +7409,7 @@
       </c>
       <c r="E279" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="E280" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="E281" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="E282" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7509,7 +7509,7 @@
       </c>
       <c r="E283" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7534,7 +7534,7 @@
       </c>
       <c r="E284" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7584,7 +7584,7 @@
       </c>
       <c r="E286" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="E287" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="E288" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="E289" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="E290" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="E291" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="E292" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7759,7 +7759,7 @@
       </c>
       <c r="E293" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7784,7 +7784,7 @@
       </c>
       <c r="E294" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="E295" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="E296" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="E297" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="E298" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="E299" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="E300" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="E301" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="E302" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="E303" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="E304" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="E305" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="E306" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8109,7 +8109,7 @@
       </c>
       <c r="E307" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="E308" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="E309" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="E310" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8209,7 +8209,7 @@
       </c>
       <c r="E311" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="E312" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="E313" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="E314" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="E315" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="E316" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="E317" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="E318" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8409,7 +8409,7 @@
       </c>
       <c r="E319" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="E320" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="E321" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="E322" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="E323" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="E324" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8559,7 +8559,7 @@
       </c>
       <c r="E325" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8584,7 +8584,7 @@
       </c>
       <c r="E326" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8609,7 +8609,7 @@
       </c>
       <c r="E327" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="E328" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="E329" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8684,7 +8684,7 @@
       </c>
       <c r="E330" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8709,7 +8709,7 @@
       </c>
       <c r="E331" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8734,7 +8734,7 @@
       </c>
       <c r="E332" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8759,7 +8759,7 @@
       </c>
       <c r="E333" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="E334" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8809,7 +8809,7 @@
       </c>
       <c r="E335" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="E336" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8859,7 +8859,7 @@
       </c>
       <c r="E337" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8884,7 +8884,7 @@
       </c>
       <c r="E338" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8909,7 +8909,7 @@
       </c>
       <c r="E339" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="E340" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="E341" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -8984,7 +8984,7 @@
       </c>
       <c r="E342" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9009,7 +9009,7 @@
       </c>
       <c r="E343" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="E344" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9059,7 +9059,7 @@
       </c>
       <c r="E345" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9084,7 +9084,7 @@
       </c>
       <c r="E346" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="E347" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="E348" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9184,7 +9184,7 @@
       </c>
       <c r="E350" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9209,7 +9209,7 @@
       </c>
       <c r="E351" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="E352" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9259,7 +9259,7 @@
       </c>
       <c r="E353" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="E354" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9309,7 +9309,7 @@
       </c>
       <c r="E355" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="E356" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="E357" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9384,7 +9384,7 @@
       </c>
       <c r="E358" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9409,7 +9409,7 @@
       </c>
       <c r="E359" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9434,7 +9434,7 @@
       </c>
       <c r="E360" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9459,7 +9459,7 @@
       </c>
       <c r="E361" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9484,7 +9484,7 @@
       </c>
       <c r="E362" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="E363" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="E364" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9559,7 +9559,7 @@
       </c>
       <c r="E365" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9584,7 +9584,7 @@
       </c>
       <c r="E366" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="E367" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9634,7 +9634,7 @@
       </c>
       <c r="E368" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9659,7 +9659,7 @@
       </c>
       <c r="E369" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9684,7 +9684,7 @@
       </c>
       <c r="E370" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="E371" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="E372" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="E373" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="E374" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="E375" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="E376" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9859,7 +9859,7 @@
       </c>
       <c r="E377" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9884,7 +9884,7 @@
       </c>
       <c r="E378" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9909,7 +9909,7 @@
       </c>
       <c r="E379" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="E380" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
       </c>
       <c r="E381" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -9984,7 +9984,7 @@
       </c>
       <c r="E382" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="E383" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10034,7 +10034,7 @@
       </c>
       <c r="E384" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10059,7 +10059,7 @@
       </c>
       <c r="E385" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="E386" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10109,7 +10109,7 @@
       </c>
       <c r="E387" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10134,7 +10134,7 @@
       </c>
       <c r="E388" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10159,7 +10159,7 @@
       </c>
       <c r="E389" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10184,7 +10184,7 @@
       </c>
       <c r="E390" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="E391" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10234,7 +10234,7 @@
       </c>
       <c r="E392" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="E393" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10284,7 +10284,7 @@
       </c>
       <c r="E394" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10309,7 +10309,7 @@
       </c>
       <c r="E395" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="E396" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10359,7 +10359,7 @@
       </c>
       <c r="E397" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="E398" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10409,7 +10409,7 @@
       </c>
       <c r="E399" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="E400" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10459,7 +10459,7 @@
       </c>
       <c r="E401" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10484,7 +10484,7 @@
       </c>
       <c r="E402" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10509,7 +10509,7 @@
       </c>
       <c r="E403" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="E404" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10559,7 +10559,7 @@
       </c>
       <c r="E405" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="E406" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10609,7 +10609,7 @@
       </c>
       <c r="E407" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="E408" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10659,7 +10659,7 @@
       </c>
       <c r="E409" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10684,7 +10684,7 @@
       </c>
       <c r="E410" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10709,7 +10709,7 @@
       </c>
       <c r="E411" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10734,7 +10734,7 @@
       </c>
       <c r="E412" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10759,7 +10759,7 @@
       </c>
       <c r="E413" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10784,7 +10784,7 @@
       </c>
       <c r="E414" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10809,7 +10809,7 @@
       </c>
       <c r="E415" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10834,7 +10834,7 @@
       </c>
       <c r="E416" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="E417" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10884,7 +10884,7 @@
       </c>
       <c r="E418" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="E419" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="E420" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10959,7 +10959,7 @@
       </c>
       <c r="E421" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -10984,7 +10984,7 @@
       </c>
       <c r="E422" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="E423" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="E424" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11059,7 +11059,7 @@
       </c>
       <c r="E425" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11084,7 +11084,7 @@
       </c>
       <c r="E426" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11109,7 +11109,7 @@
       </c>
       <c r="E427" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11134,7 +11134,7 @@
       </c>
       <c r="E428" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11159,7 +11159,7 @@
       </c>
       <c r="E429" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11184,7 +11184,7 @@
       </c>
       <c r="E430" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11209,7 +11209,7 @@
       </c>
       <c r="E431" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="E432" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11259,7 @@
       </c>
       <c r="E433" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11284,7 +11284,7 @@
       </c>
       <c r="E434" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11309,7 +11309,7 @@
       </c>
       <c r="E435" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11334,7 +11334,7 @@
       </c>
       <c r="E436" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="E437" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11384,7 +11384,7 @@
       </c>
       <c r="E438" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11409,7 +11409,7 @@
       </c>
       <c r="E439" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11434,7 +11434,7 @@
       </c>
       <c r="E440" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11459,7 +11459,7 @@
       </c>
       <c r="E441" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11484,7 +11484,7 @@
       </c>
       <c r="E442" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11509,7 +11509,7 @@
       </c>
       <c r="E443" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11534,7 +11534,7 @@
       </c>
       <c r="E444" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11559,7 +11559,7 @@
       </c>
       <c r="E445" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11584,7 +11584,7 @@
       </c>
       <c r="E446" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="E447" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11634,7 +11634,7 @@
       </c>
       <c r="E448" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="E449" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11684,7 +11684,7 @@
       </c>
       <c r="E450" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="E451" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="E452" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11759,7 +11759,7 @@
       </c>
       <c r="E453" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="E454" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="E455" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11834,7 +11834,7 @@
       </c>
       <c r="E456" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="E457" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="E458" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11909,7 +11909,7 @@
       </c>
       <c r="E459" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="E460" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11959,7 +11959,7 @@
       </c>
       <c r="E461" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -11984,7 +11984,7 @@
       </c>
       <c r="E462" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12009,7 +12009,7 @@
       </c>
       <c r="E463" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="E464" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12059,7 +12059,7 @@
       </c>
       <c r="E465" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12084,7 +12084,7 @@
       </c>
       <c r="E466" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12109,7 +12109,7 @@
       </c>
       <c r="E467" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12134,7 +12134,7 @@
       </c>
       <c r="E468" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12159,7 +12159,7 @@
       </c>
       <c r="E469" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12184,7 +12184,7 @@
       </c>
       <c r="E470" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12209,7 +12209,7 @@
       </c>
       <c r="E471" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12234,7 +12234,7 @@
       </c>
       <c r="E472" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12259,7 +12259,7 @@
       </c>
       <c r="E473" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12284,7 +12284,7 @@
       </c>
       <c r="E474" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12309,7 +12309,7 @@
       </c>
       <c r="E475" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12334,7 +12334,7 @@
       </c>
       <c r="E476" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12359,7 +12359,7 @@
       </c>
       <c r="E477" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12384,7 +12384,7 @@
       </c>
       <c r="E478" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12409,7 +12409,7 @@
       </c>
       <c r="E479" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12434,7 +12434,7 @@
       </c>
       <c r="E480" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="E481" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12484,7 +12484,7 @@
       </c>
       <c r="E482" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12509,7 +12509,7 @@
       </c>
       <c r="E483" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12534,7 @@
       </c>
       <c r="E484" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="E485" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12584,7 +12584,7 @@
       </c>
       <c r="E486" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12609,7 +12609,7 @@
       </c>
       <c r="E487" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="E488" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="E489" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12684,7 +12684,7 @@
       </c>
       <c r="E490" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12709,7 +12709,7 @@
       </c>
       <c r="E491" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12734,7 +12734,7 @@
       </c>
       <c r="E492" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="E493" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12784,7 +12784,7 @@
       </c>
       <c r="E494" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12809,7 +12809,7 @@
       </c>
       <c r="E495" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12834,7 +12834,7 @@
       </c>
       <c r="E496" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="E497" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="E498" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12909,7 +12909,7 @@
       </c>
       <c r="E499" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12934,7 +12934,7 @@
       </c>
       <c r="E500" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12959,7 +12959,7 @@
       </c>
       <c r="E501" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -12984,7 +12984,7 @@
       </c>
       <c r="E502" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13009,7 +13009,7 @@
       </c>
       <c r="E503" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13034,7 +13034,7 @@
       </c>
       <c r="E504" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13059,7 +13059,7 @@
       </c>
       <c r="E505" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13084,7 +13084,7 @@
       </c>
       <c r="E506" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13109,7 +13109,7 @@
       </c>
       <c r="E507" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13134,7 +13134,7 @@
       </c>
       <c r="E508" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13159,7 +13159,7 @@
       </c>
       <c r="E509" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="E510" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13209,7 +13209,7 @@
       </c>
       <c r="E511" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13234,7 +13234,7 @@
       </c>
       <c r="E512" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13259,7 +13259,7 @@
       </c>
       <c r="E513" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13284,7 +13284,7 @@
       </c>
       <c r="E514" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13309,7 +13309,7 @@
       </c>
       <c r="E515" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="E516" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13359,7 +13359,7 @@
       </c>
       <c r="E517" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13384,7 +13384,7 @@
       </c>
       <c r="E518" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13409,7 +13409,7 @@
       </c>
       <c r="E519" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13434,7 +13434,7 @@
       </c>
       <c r="E520" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13459,7 +13459,7 @@
       </c>
       <c r="E521" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13484,7 +13484,7 @@
       </c>
       <c r="E522" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="E523" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13534,7 +13534,7 @@
       </c>
       <c r="E524" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13559,7 +13559,7 @@
       </c>
       <c r="E525" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13584,7 +13584,7 @@
       </c>
       <c r="E526" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13609,7 +13609,7 @@
       </c>
       <c r="E527" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="E528" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13659,7 +13659,7 @@
       </c>
       <c r="E529" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13684,7 +13684,7 @@
       </c>
       <c r="E530" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13709,7 +13709,7 @@
       </c>
       <c r="E531" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13734,7 +13734,7 @@
       </c>
       <c r="E532" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13759,7 +13759,7 @@
       </c>
       <c r="E533" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13784,7 +13784,7 @@
       </c>
       <c r="E534" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13809,7 +13809,7 @@
       </c>
       <c r="E535" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13834,7 +13834,7 @@
       </c>
       <c r="E536" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13859,7 +13859,7 @@
       </c>
       <c r="E537" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13884,7 +13884,7 @@
       </c>
       <c r="E538" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13909,7 +13909,7 @@
       </c>
       <c r="E539" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13934,7 +13934,7 @@
       </c>
       <c r="E540" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13959,7 +13959,7 @@
       </c>
       <c r="E541" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -13984,7 +13984,7 @@
       </c>
       <c r="E542" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14009,7 +14009,7 @@
       </c>
       <c r="E543" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="E544" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14059,7 +14059,7 @@
       </c>
       <c r="E545" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14084,7 +14084,7 @@
       </c>
       <c r="E546" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="E547" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14134,7 +14134,7 @@
       </c>
       <c r="E548" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="E549" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14184,7 +14184,7 @@
       </c>
       <c r="E550" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14209,7 +14209,7 @@
       </c>
       <c r="E551" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14234,7 +14234,7 @@
       </c>
       <c r="E552" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14259,7 +14259,7 @@
       </c>
       <c r="E553" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="E554" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14309,7 +14309,7 @@
       </c>
       <c r="E555" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14334,7 +14334,7 @@
       </c>
       <c r="E556" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14359,7 +14359,7 @@
       </c>
       <c r="E557" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14384,7 +14384,7 @@
       </c>
       <c r="E558" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14409,7 @@
       </c>
       <c r="E559" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14434,7 +14434,7 @@
       </c>
       <c r="E560" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14459,7 +14459,7 @@
       </c>
       <c r="E561" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="E562" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14509,7 +14509,7 @@
       </c>
       <c r="E563" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="E564" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14559,7 +14559,7 @@
       </c>
       <c r="E565" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14584,7 +14584,7 @@
       </c>
       <c r="E566" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14609,7 +14609,7 @@
       </c>
       <c r="E567" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14634,7 +14634,7 @@
       </c>
       <c r="E568" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14659,7 +14659,7 @@
       </c>
       <c r="E569" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14684,7 +14684,7 @@
       </c>
       <c r="E570" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14709,7 +14709,7 @@
       </c>
       <c r="E571" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="E572" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14759,7 +14759,7 @@
       </c>
       <c r="E573" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="E574" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="E575" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="E576" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14859,7 +14859,7 @@
       </c>
       <c r="E577" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14884,7 +14884,7 @@
       </c>
       <c r="E578" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14909,7 +14909,7 @@
       </c>
       <c r="E579" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14934,7 +14934,7 @@
       </c>
       <c r="E580" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14959,7 +14959,7 @@
       </c>
       <c r="E581" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="E582" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15009,7 +15009,7 @@
       </c>
       <c r="E583" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15034,7 +15034,7 @@
       </c>
       <c r="E584" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15059,7 +15059,7 @@
       </c>
       <c r="E585" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15084,7 +15084,7 @@
       </c>
       <c r="E586" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15109,7 +15109,7 @@
       </c>
       <c r="E587" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="E588" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15159,7 +15159,7 @@
       </c>
       <c r="E589" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15184,7 +15184,7 @@
       </c>
       <c r="E590" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15209,7 +15209,7 @@
       </c>
       <c r="E591" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15234,7 +15234,7 @@
       </c>
       <c r="E592" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15259,7 +15259,7 @@
       </c>
       <c r="E593" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15284,7 +15284,7 @@
       </c>
       <c r="E594" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15309,7 +15309,7 @@
       </c>
       <c r="E595" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15334,7 +15334,7 @@
       </c>
       <c r="E596" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15359,7 +15359,7 @@
       </c>
       <c r="E597" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15384,7 +15384,7 @@
       </c>
       <c r="E598" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="E599" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="E600" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15459,7 @@
       </c>
       <c r="E601" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="E602" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15509,7 +15509,7 @@
       </c>
       <c r="E603" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15534,7 +15534,7 @@
       </c>
       <c r="E604" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15559,7 +15559,7 @@
       </c>
       <c r="E605" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15584,7 +15584,7 @@
       </c>
       <c r="E606" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15609,7 +15609,7 @@
       </c>
       <c r="E607" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15634,7 +15634,7 @@
       </c>
       <c r="E608" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15659,7 +15659,7 @@
       </c>
       <c r="E609" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15684,7 +15684,7 @@
       </c>
       <c r="E610" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15709,7 +15709,7 @@
       </c>
       <c r="E611" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="E612" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15759,7 +15759,7 @@
       </c>
       <c r="E613" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15784,7 +15784,7 @@
       </c>
       <c r="E614" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15809,7 +15809,7 @@
       </c>
       <c r="E615" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15834,7 +15834,7 @@
       </c>
       <c r="E616" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15859,7 +15859,7 @@
       </c>
       <c r="E617" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="E618" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15909,7 +15909,7 @@
       </c>
       <c r="E619" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15934,7 +15934,7 @@
       </c>
       <c r="E620" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15959,7 +15959,7 @@
       </c>
       <c r="E621" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="E622" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16009,7 +16009,7 @@
       </c>
       <c r="E623" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16034,7 +16034,7 @@
       </c>
       <c r="E624" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16059,7 +16059,7 @@
       </c>
       <c r="E625" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16084,7 +16084,7 @@
       </c>
       <c r="E626" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16109,7 +16109,7 @@
       </c>
       <c r="E627" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="E628" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="E629" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16184,7 +16184,7 @@
       </c>
       <c r="E630" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16209,7 +16209,7 @@
       </c>
       <c r="E631" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16234,7 +16234,7 @@
       </c>
       <c r="E632" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16259,7 +16259,7 @@
       </c>
       <c r="E633" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16284,7 +16284,7 @@
       </c>
       <c r="E634" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16309,7 +16309,7 @@
       </c>
       <c r="E635" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16334,7 +16334,7 @@
       </c>
       <c r="E636" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16359,7 +16359,7 @@
       </c>
       <c r="E637" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16384,7 +16384,7 @@
       </c>
       <c r="E638" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16409,7 +16409,7 @@
       </c>
       <c r="E639" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="E640" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16459,7 +16459,7 @@
       </c>
       <c r="E641" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16484,7 +16484,7 @@
       </c>
       <c r="E642" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16509,7 +16509,7 @@
       </c>
       <c r="E643" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16534,7 +16534,7 @@
       </c>
       <c r="E644" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="E645" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16584,7 +16584,7 @@
       </c>
       <c r="E646" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16609,7 +16609,7 @@
       </c>
       <c r="E647" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="E648" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16659,7 +16659,7 @@
       </c>
       <c r="E649" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16684,7 +16684,7 @@
       </c>
       <c r="E650" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16709,7 +16709,7 @@
       </c>
       <c r="E651" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16734,7 +16734,7 @@
       </c>
       <c r="E652" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16759,7 +16759,7 @@
       </c>
       <c r="E653" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="E654" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="E655" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="E656" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16859,7 +16859,7 @@
       </c>
       <c r="E657" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16884,7 +16884,7 @@
       </c>
       <c r="E658" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16909,7 +16909,7 @@
       </c>
       <c r="E659" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16934,7 +16934,7 @@
       </c>
       <c r="E660" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16959,7 +16959,7 @@
       </c>
       <c r="E661" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -16984,7 +16984,7 @@
       </c>
       <c r="E662" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17009,7 +17009,7 @@
       </c>
       <c r="E663" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17034,7 +17034,7 @@
       </c>
       <c r="E664" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17059,7 +17059,7 @@
       </c>
       <c r="E665" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17084,7 +17084,7 @@
       </c>
       <c r="E666" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17109,7 +17109,7 @@
       </c>
       <c r="E667" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17134,7 +17134,7 @@
       </c>
       <c r="E668" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17159,7 +17159,7 @@
       </c>
       <c r="E669" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="E670" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17209,7 +17209,7 @@
       </c>
       <c r="E671" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17234,7 +17234,7 @@
       </c>
       <c r="E672" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17259,7 +17259,7 @@
       </c>
       <c r="E673" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17284,7 +17284,7 @@
       </c>
       <c r="E674" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17309,7 +17309,7 @@
       </c>
       <c r="E675" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17334,7 +17334,7 @@
       </c>
       <c r="E676" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17359,7 +17359,7 @@
       </c>
       <c r="E677" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17384,7 +17384,7 @@
       </c>
       <c r="E678" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="E679" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17434,7 +17434,7 @@
       </c>
       <c r="E680" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17459,7 +17459,7 @@
       </c>
       <c r="E681" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="E682" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17509,7 +17509,7 @@
       </c>
       <c r="E683" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="E684" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17559,7 +17559,7 @@
       </c>
       <c r="E685" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17584,7 +17584,7 @@
       </c>
       <c r="E686" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17609,7 +17609,7 @@
       </c>
       <c r="E687" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="E688" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17659,7 +17659,7 @@
       </c>
       <c r="E689" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17684,7 +17684,7 @@
       </c>
       <c r="E690" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17709,7 +17709,7 @@
       </c>
       <c r="E691" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17734,7 +17734,7 @@
       </c>
       <c r="E692" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="E693" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17784,7 +17784,7 @@
       </c>
       <c r="E694" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17809,7 +17809,7 @@
       </c>
       <c r="E695" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17834,7 +17834,7 @@
       </c>
       <c r="E696" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17859,7 +17859,7 @@
       </c>
       <c r="E697" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17884,7 +17884,7 @@
       </c>
       <c r="E698" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17909,7 +17909,7 @@
       </c>
       <c r="E699" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17934,7 +17934,7 @@
       </c>
       <c r="E700" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17959,7 +17959,7 @@
       </c>
       <c r="E701" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -17984,7 +17984,7 @@
       </c>
       <c r="E702" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18009,7 +18009,7 @@
       </c>
       <c r="E703" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18034,7 +18034,7 @@
       </c>
       <c r="E704" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18059,7 +18059,7 @@
       </c>
       <c r="E705" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18084,7 +18084,7 @@
       </c>
       <c r="E706" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18109,7 +18109,7 @@
       </c>
       <c r="E707" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18134,7 +18134,7 @@
       </c>
       <c r="E708" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18159,7 +18159,7 @@
       </c>
       <c r="E709" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18184,7 +18184,7 @@
       </c>
       <c r="E710" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18209,7 +18209,7 @@
       </c>
       <c r="E711" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="E712" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18259,7 +18259,7 @@
       </c>
       <c r="E713" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18284,7 +18284,7 @@
       </c>
       <c r="E714" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18309,7 +18309,7 @@
       </c>
       <c r="E715" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18334,7 +18334,7 @@
       </c>
       <c r="E716" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18359,7 +18359,7 @@
       </c>
       <c r="E717" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18384,7 +18384,7 @@
       </c>
       <c r="E718" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18409,7 +18409,7 @@
       </c>
       <c r="E719" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18434,7 +18434,7 @@
       </c>
       <c r="E720" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18459,7 +18459,7 @@
       </c>
       <c r="E721" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18484,7 +18484,7 @@
       </c>
       <c r="E722" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18509,7 +18509,7 @@
       </c>
       <c r="E723" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18534,7 +18534,7 @@
       </c>
       <c r="E724" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18559,7 +18559,7 @@
       </c>
       <c r="E725" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18584,7 +18584,7 @@
       </c>
       <c r="E726" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18609,7 +18609,7 @@
       </c>
       <c r="E727" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18634,7 +18634,7 @@
       </c>
       <c r="E728" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18659,7 +18659,7 @@
       </c>
       <c r="E729" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18684,7 +18684,7 @@
       </c>
       <c r="E730" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="E731" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18734,7 +18734,7 @@
       </c>
       <c r="E732" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18759,7 +18759,7 @@
       </c>
       <c r="E733" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18784,7 +18784,7 @@
       </c>
       <c r="E734" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="E735" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18834,7 +18834,7 @@
       </c>
       <c r="E736" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18859,7 +18859,7 @@
       </c>
       <c r="E737" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18884,7 +18884,7 @@
       </c>
       <c r="E738" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18909,7 +18909,7 @@
       </c>
       <c r="E739" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="E740" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18959,7 +18959,7 @@
       </c>
       <c r="E741" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -18984,7 +18984,7 @@
       </c>
       <c r="E742" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19009,7 +19009,7 @@
       </c>
       <c r="E743" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="E744" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19059,7 +19059,7 @@
       </c>
       <c r="E745" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19084,7 +19084,7 @@
       </c>
       <c r="E746" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19109,7 +19109,7 @@
       </c>
       <c r="E747" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19134,7 +19134,7 @@
       </c>
       <c r="E748" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19159,7 +19159,7 @@
       </c>
       <c r="E749" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19184,7 +19184,7 @@
       </c>
       <c r="E750" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="E751" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19234,7 +19234,7 @@
       </c>
       <c r="E752" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19259,7 +19259,7 @@
       </c>
       <c r="E753" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19284,7 +19284,7 @@
       </c>
       <c r="E754" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19309,7 +19309,7 @@
       </c>
       <c r="E755" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19334,7 +19334,7 @@
       </c>
       <c r="E756" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="E757" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19384,7 +19384,7 @@
       </c>
       <c r="E758" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19409,7 +19409,7 @@
       </c>
       <c r="E759" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19434,7 +19434,7 @@
       </c>
       <c r="E760" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19459,7 +19459,7 @@
       </c>
       <c r="E761" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19484,7 +19484,7 @@
       </c>
       <c r="E762" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19509,7 +19509,7 @@
       </c>
       <c r="E763" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19534,7 +19534,7 @@
       </c>
       <c r="E764" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="E765" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19584,7 +19584,7 @@
       </c>
       <c r="E766" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19609,7 +19609,7 @@
       </c>
       <c r="E767" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="E768" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19659,7 +19659,7 @@
       </c>
       <c r="E769" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="E770" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19709,7 +19709,7 @@
       </c>
       <c r="E771" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19734,7 +19734,7 @@
       </c>
       <c r="E772" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="E773" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19784,7 +19784,7 @@
       </c>
       <c r="E774" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19809,7 +19809,7 @@
       </c>
       <c r="E775" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19834,7 +19834,7 @@
       </c>
       <c r="E776" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19859,7 +19859,7 @@
       </c>
       <c r="E777" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="E778" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19909,7 +19909,7 @@
       </c>
       <c r="E779" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19934,7 +19934,7 @@
       </c>
       <c r="E780" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19959,7 +19959,7 @@
       </c>
       <c r="E781" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -19984,7 +19984,7 @@
       </c>
       <c r="E782" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20009,7 +20009,7 @@
       </c>
       <c r="E783" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20034,7 +20034,7 @@
       </c>
       <c r="E784" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="E785" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20084,7 +20084,7 @@
       </c>
       <c r="E786" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20109,7 +20109,7 @@
       </c>
       <c r="E787" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20134,7 +20134,7 @@
       </c>
       <c r="E788" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20159,7 +20159,7 @@
       </c>
       <c r="E789" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20184,7 +20184,7 @@
       </c>
       <c r="E790" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20209,7 +20209,7 @@
       </c>
       <c r="E791" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20234,7 +20234,7 @@
       </c>
       <c r="E792" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20259,7 +20259,7 @@
       </c>
       <c r="E793" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20284,7 +20284,7 @@
       </c>
       <c r="E794" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20309,7 +20309,7 @@
       </c>
       <c r="E795" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="E796" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20359,7 +20359,7 @@
       </c>
       <c r="E797" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="E798" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20409,7 +20409,7 @@
       </c>
       <c r="E799" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20434,7 +20434,7 @@
       </c>
       <c r="E800" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20459,7 +20459,7 @@
       </c>
       <c r="E801" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20484,7 +20484,7 @@
       </c>
       <c r="E802" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20509,7 +20509,7 @@
       </c>
       <c r="E803" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20534,7 +20534,7 @@
       </c>
       <c r="E804" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20559,7 +20559,7 @@
       </c>
       <c r="E805" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20584,7 +20584,7 @@
       </c>
       <c r="E806" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20609,7 +20609,7 @@
       </c>
       <c r="E807" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20634,7 +20634,7 @@
       </c>
       <c r="E808" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="E809" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20684,7 +20684,7 @@
       </c>
       <c r="E810" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20709,7 +20709,7 @@
       </c>
       <c r="E811" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="E812" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20759,7 +20759,7 @@
       </c>
       <c r="E813" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20784,7 +20784,7 @@
       </c>
       <c r="E814" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20809,7 +20809,7 @@
       </c>
       <c r="E815" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="E816" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20859,7 +20859,7 @@
       </c>
       <c r="E817" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20884,7 +20884,7 @@
       </c>
       <c r="E818" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20909,7 +20909,7 @@
       </c>
       <c r="E819" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20934,7 +20934,7 @@
       </c>
       <c r="E820" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20959,7 +20959,7 @@
       </c>
       <c r="E821" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -20984,7 +20984,7 @@
       </c>
       <c r="E822" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21009,7 +21009,7 @@
       </c>
       <c r="E823" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="E824" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21059,7 +21059,7 @@
       </c>
       <c r="E825" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21084,7 +21084,7 @@
       </c>
       <c r="E826" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21109,7 +21109,7 @@
       </c>
       <c r="E827" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21134,7 +21134,7 @@
       </c>
       <c r="E828" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21159,7 +21159,7 @@
       </c>
       <c r="E829" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21184,7 +21184,7 @@
       </c>
       <c r="E830" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21234,7 +21234,7 @@
       </c>
       <c r="E832" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21259,7 +21259,7 @@
       </c>
       <c r="E833" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21284,7 +21284,7 @@
       </c>
       <c r="E834" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21309,7 +21309,7 @@
       </c>
       <c r="E835" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21334,7 +21334,7 @@
       </c>
       <c r="E836" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21359,7 +21359,7 @@
       </c>
       <c r="E837" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21384,7 +21384,7 @@
       </c>
       <c r="E838" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21409,7 +21409,7 @@
       </c>
       <c r="E839" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21434,7 +21434,7 @@
       </c>
       <c r="E840" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21459,7 +21459,7 @@
       </c>
       <c r="E841" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21484,7 +21484,7 @@
       </c>
       <c r="E842" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21509,7 +21509,7 @@
       </c>
       <c r="E843" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21534,7 +21534,7 @@
       </c>
       <c r="E844" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21559,7 +21559,7 @@
       </c>
       <c r="E845" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21584,7 +21584,7 @@
       </c>
       <c r="E846" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21609,7 +21609,7 @@
       </c>
       <c r="E847" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21634,7 +21634,7 @@
       </c>
       <c r="E848" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21659,7 +21659,7 @@
       </c>
       <c r="E849" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21684,7 +21684,7 @@
       </c>
       <c r="E850" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="E851" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="E852" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21759,7 +21759,7 @@
       </c>
       <c r="E853" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21784,7 +21784,7 @@
       </c>
       <c r="E854" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21809,7 +21809,7 @@
       </c>
       <c r="E855" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21834,7 +21834,7 @@
       </c>
       <c r="E856" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21859,7 +21859,7 @@
       </c>
       <c r="E857" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21884,7 +21884,7 @@
       </c>
       <c r="E858" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21909,7 +21909,7 @@
       </c>
       <c r="E859" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21959,7 +21959,7 @@
       </c>
       <c r="E861" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -21984,7 +21984,7 @@
       </c>
       <c r="E862" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22034,7 +22034,7 @@
       </c>
       <c r="E864" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22059,7 +22059,7 @@
       </c>
       <c r="E865" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22084,7 +22084,7 @@
       </c>
       <c r="E866" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22109,7 +22109,7 @@
       </c>
       <c r="E867" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22159,7 +22159,7 @@
       </c>
       <c r="E869" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22184,7 +22184,7 @@
       </c>
       <c r="E870" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22209,7 +22209,7 @@
       </c>
       <c r="E871" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22234,7 +22234,7 @@
       </c>
       <c r="E872" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22259,7 +22259,7 @@
       </c>
       <c r="E873" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22284,7 +22284,7 @@
       </c>
       <c r="E874" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22309,7 +22309,7 @@
       </c>
       <c r="E875" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22334,7 +22334,7 @@
       </c>
       <c r="E876" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22359,7 +22359,7 @@
       </c>
       <c r="E877" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22384,7 +22384,7 @@
       </c>
       <c r="E878" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22409,7 +22409,7 @@
       </c>
       <c r="E879" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="E880" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22459,7 +22459,7 @@
       </c>
       <c r="E881" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22484,7 +22484,7 @@
       </c>
       <c r="E882" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22509,7 +22509,7 @@
       </c>
       <c r="E883" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22534,7 +22534,7 @@
       </c>
       <c r="E884" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22559,7 +22559,7 @@
       </c>
       <c r="E885" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22584,7 +22584,7 @@
       </c>
       <c r="E886" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22609,7 +22609,7 @@
       </c>
       <c r="E887" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22634,7 +22634,7 @@
       </c>
       <c r="E888" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22659,7 +22659,7 @@
       </c>
       <c r="E889" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22684,7 +22684,7 @@
       </c>
       <c r="E890" s="3" t="inlineStr">
         <is>
-          <t>21-02-26</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22709,7 +22709,7 @@
       </c>
       <c r="E891" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22734,7 +22734,7 @@
       </c>
       <c r="E892" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22759,7 +22759,7 @@
       </c>
       <c r="E893" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22784,7 +22784,7 @@
       </c>
       <c r="E894" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22809,7 +22809,7 @@
       </c>
       <c r="E895" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22834,7 +22834,7 @@
       </c>
       <c r="E896" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22859,7 +22859,7 @@
       </c>
       <c r="E897" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22884,7 +22884,7 @@
       </c>
       <c r="E898" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22909,7 +22909,7 @@
       </c>
       <c r="E899" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22934,7 +22934,7 @@
       </c>
       <c r="E900" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22959,7 +22959,7 @@
       </c>
       <c r="E901" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -22984,7 +22984,7 @@
       </c>
       <c r="E902" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23009,7 +23009,7 @@
       </c>
       <c r="E903" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23034,7 +23034,7 @@
       </c>
       <c r="E904" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23059,7 +23059,7 @@
       </c>
       <c r="E905" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23084,7 +23084,7 @@
       </c>
       <c r="E906" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23109,7 +23109,7 @@
       </c>
       <c r="E907" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="E908" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23159,7 +23159,7 @@
       </c>
       <c r="E909" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23184,7 +23184,7 @@
       </c>
       <c r="E910" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23209,7 +23209,7 @@
       </c>
       <c r="E911" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23309,7 +23309,7 @@
       </c>
       <c r="E915" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23384,7 +23384,7 @@
       </c>
       <c r="E918" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23409,7 +23409,7 @@
       </c>
       <c r="E919" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23434,7 +23434,7 @@
       </c>
       <c r="E920" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23459,7 +23459,7 @@
       </c>
       <c r="E921" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23484,7 +23484,7 @@
       </c>
       <c r="E922" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23509,7 +23509,7 @@
       </c>
       <c r="E923" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23534,7 +23534,7 @@
       </c>
       <c r="E924" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23559,7 +23559,7 @@
       </c>
       <c r="E925" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23584,7 +23584,7 @@
       </c>
       <c r="E926" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23609,7 +23609,7 @@
       </c>
       <c r="E927" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23634,7 +23634,7 @@
       </c>
       <c r="E928" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23659,7 +23659,7 @@
       </c>
       <c r="E929" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23684,7 +23684,7 @@
       </c>
       <c r="E930" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23709,7 +23709,7 @@
       </c>
       <c r="E931" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23734,7 +23734,7 @@
       </c>
       <c r="E932" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23759,7 +23759,7 @@
       </c>
       <c r="E933" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23784,7 +23784,7 @@
       </c>
       <c r="E934" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23809,7 +23809,7 @@
       </c>
       <c r="E935" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="E936" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23859,7 +23859,7 @@
       </c>
       <c r="E937" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23884,7 +23884,7 @@
       </c>
       <c r="E938" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23909,7 +23909,7 @@
       </c>
       <c r="E939" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23934,7 +23934,7 @@
       </c>
       <c r="E940" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23959,7 +23959,7 @@
       </c>
       <c r="E941" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -23984,7 +23984,7 @@
       </c>
       <c r="E942" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24009,7 +24009,7 @@
       </c>
       <c r="E943" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24034,7 +24034,7 @@
       </c>
       <c r="E944" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24059,7 +24059,7 @@
       </c>
       <c r="E945" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24084,7 +24084,7 @@
       </c>
       <c r="E946" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="E947" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24134,7 +24134,7 @@
       </c>
       <c r="E948" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24159,7 +24159,7 @@
       </c>
       <c r="E949" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24184,7 +24184,7 @@
       </c>
       <c r="E950" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24209,7 +24209,7 @@
       </c>
       <c r="E951" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="E952" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24259,7 +24259,7 @@
       </c>
       <c r="E953" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24284,7 +24284,7 @@
       </c>
       <c r="E954" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24309,7 +24309,7 @@
       </c>
       <c r="E955" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24334,7 +24334,7 @@
       </c>
       <c r="E956" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24359,7 +24359,7 @@
       </c>
       <c r="E957" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24384,7 +24384,7 @@
       </c>
       <c r="E958" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24409,7 +24409,7 @@
       </c>
       <c r="E959" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24434,7 +24434,7 @@
       </c>
       <c r="E960" s="3" t="inlineStr">
         <is>
-          <t>25-06-27</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24459,7 +24459,7 @@
       </c>
       <c r="E961" s="3" t="inlineStr">
         <is>
-          <t>26-04-22</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24484,7 +24484,7 @@
       </c>
       <c r="E962" s="3" t="inlineStr">
         <is>
-          <t>26-04-22</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24509,7 +24509,7 @@
       </c>
       <c r="E963" s="3" t="inlineStr">
         <is>
-          <t>26-04-22</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="E964" s="3" t="inlineStr">
         <is>
-          <t>26-04-22</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24559,7 +24559,7 @@
       </c>
       <c r="E965" s="3" t="inlineStr">
         <is>
-          <t>26-04-22</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24584,7 +24584,7 @@
       </c>
       <c r="E966" s="3" t="inlineStr">
         <is>
-          <t>26-04-22</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24609,7 +24609,7 @@
       </c>
       <c r="E967" s="3" t="inlineStr">
         <is>
-          <t>26-04-22</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24634,7 +24634,7 @@
       </c>
       <c r="E968" s="3" t="inlineStr">
         <is>
-          <t>26-04-22</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24659,7 +24659,7 @@
       </c>
       <c r="E969" s="3" t="inlineStr">
         <is>
-          <t>26-04-22</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24684,7 +24684,7 @@
       </c>
       <c r="E970" s="3" t="inlineStr">
         <is>
-          <t>26-04-22</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
@@ -24709,7 +24709,7 @@
       </c>
       <c r="E971" s="3" t="inlineStr">
         <is>
-          <t>26-04-22</t>
+          <t>26-05-07</t>
         </is>
       </c>
     </row>
